--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -115,20 +115,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -540,14 +537,14 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edita sólo las columnas amarillas: Coste nuevo, A, D, V, Rasgo y Texto del rasgo. Los costes son enteros de 0 a 8 (ej. 2); A, D y V, de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran.</t>
+          <t>Edita las columnas amarillas: Rareza, Coste nuevo, A, D, V, Rasgo y Texto del rasgo. La rareza se elige del desplegable; los costes son enteros de 0 a 8 (ej. 2) y A, D y V van de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran al aplicar.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>No cambies el id, no borres ni añadas filas y no reordenes: el id es la llave con la que cada fila vuelve a su carta. Los eventos, climas y recursos no tienen A/D/V y se quedan en blanco.</t>
+          <t>No cambies el id, no borres ni añadas filas y no reordenes: el id es la llave con la que cada fila vuelve a su carta. Los eventos, climas y recursos no tienen A/D/V y se quedan en blanco. Cambiar la rareza mueve las copias que caben en un mazo, lo que sale en los sobres y la fusión.</t>
         </is>
       </c>
     </row>
@@ -629,31 +626,31 @@
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="F6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
         <f>IF(F6="","",F6-E6)</f>
         <v/>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="H6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
@@ -680,31 +677,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <f>IF(F7="","",F7-E7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <f>IF(F7="","",F7-E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Oportunista</t>
         </is>
@@ -731,31 +728,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
+        <f>IF(F8="","",F8-E8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
-        <f>IF(F8="","",F8-E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
@@ -782,31 +779,31 @@
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="F9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6">
         <f>IF(F9="","",F9-E9)</f>
         <v/>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Tagomizador</t>
         </is>
@@ -833,31 +830,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6">
+        <f>IF(F10="","",F10-E10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="5">
-        <f>IF(F10="","",F10-E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Depredador dominante</t>
         </is>
@@ -884,31 +881,31 @@
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="F11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="6">
         <f>IF(F11="","",F11-E11)</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Migrador</t>
         </is>
@@ -935,31 +932,31 @@
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
         <f>IF(F12="","",F12-E12)</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Ramoneo bajo</t>
         </is>
@@ -986,31 +983,31 @@
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="5">
+      <c r="F13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="6">
         <f>IF(F13="","",F13-E13)</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Masa colosal</t>
         </is>
@@ -1037,31 +1034,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="5">
+      <c r="F14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="6">
         <f>IF(F14="","",F14-E14)</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6" t="n">
+      <c r="I14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Escaso</t>
         </is>
@@ -1088,31 +1085,31 @@
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6">
+        <f>IF(F15="","",F15-E15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5">
-        <f>IF(F15="","",F15-E15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Coraza dorsal</t>
         </is>
@@ -1139,31 +1136,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="6">
+        <f>IF(F16="","",F16-E16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(F16="","",F16-E16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
@@ -1190,31 +1187,31 @@
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="5">
+      <c r="F17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="6">
         <f>IF(F17="","",F17-E17)</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Gola ornamentada</t>
         </is>
@@ -1241,31 +1238,31 @@
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="E18" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="F18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="6">
         <f>IF(F18="","",F18-E18)</f>
         <v/>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="6" t="n">
+      <c r="I18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
@@ -1292,31 +1289,31 @@
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="5">
+      <c r="F19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="6">
         <f>IF(F19="","",F19-E19)</f>
         <v/>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="6" t="n">
+      <c r="I19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Desgarro</t>
         </is>
@@ -1343,31 +1340,31 @@
           <t>Pterosaurio</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="6" t="n">
+      <c r="E20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="5">
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="6">
         <f>IF(F20="","",F20-E20)</f>
         <v/>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
@@ -1394,25 +1391,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="E21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
         <f>IF(F21="","",F21-E21)</f>
         <v/>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
@@ -1439,25 +1436,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="E22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
         <f>IF(F22="","",F22-E22)</f>
         <v/>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
@@ -1484,25 +1481,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5">
+      <c r="E23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
         <f>IF(F23="","",F23-E23)</f>
         <v/>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
@@ -1529,25 +1526,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
         <f>IF(F24="","",F24-E24)</f>
         <v/>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
@@ -1574,25 +1571,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="E25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
         <f>IF(F25="","",F25-E25)</f>
         <v/>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
@@ -1619,25 +1616,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="E26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
         <f>IF(F26="","",F26-E26)</f>
         <v/>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
@@ -1664,25 +1661,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="E27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6">
         <f>IF(F27="","",F27-E27)</f>
         <v/>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
@@ -1709,25 +1706,25 @@
           <t>Evento</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="E28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="6">
         <f>IF(F28="","",F28-E28)</f>
         <v/>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
@@ -1754,25 +1751,25 @@
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="6">
         <f>IF(F29="","",F29-E29)</f>
         <v/>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
@@ -1799,25 +1796,25 @@
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="6">
         <f>IF(F30="","",F30-E30)</f>
         <v/>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
@@ -1844,25 +1841,25 @@
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="6">
         <f>IF(F31="","",F31-E31)</f>
         <v/>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
@@ -1889,25 +1886,25 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5">
+      <c r="E32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6">
         <f>IF(F32="","",F32-E32)</f>
         <v/>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
@@ -1934,25 +1931,25 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5">
+      <c r="E33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6">
         <f>IF(F33="","",F33-E33)</f>
         <v/>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
@@ -1979,25 +1976,25 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5">
+      <c r="E34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6">
         <f>IF(F34="","",F34-E34)</f>
         <v/>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
@@ -2024,25 +2021,25 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5">
+      <c r="E35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6">
         <f>IF(F35="","",F35-E35)</f>
         <v/>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
@@ -2069,25 +2066,25 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5">
+      <c r="E36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6">
         <f>IF(F36="","",F36-E36)</f>
         <v/>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
@@ -2099,13 +2096,12 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <autoFilter ref="A5:L36"/>
   <mergeCells count="2">
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="F6:F36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
@@ -2113,6 +2109,9 @@
     <dataValidation sqref="H6:J36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque, Defensa y Vida van de 0 a 20." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
+    </dataValidation>
+    <dataValidation sqref="D6:D36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
+      <formula1>"Común,Rara,Épica,Legendaria"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2126,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2152,21 +2151,21 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>&gt; La genera y la aplica `node tools/tabla.mjs`. **Edita sólo las columnas</t>
+          <t>&gt; La genera y la aplica `node tools/tabla.mjs`. **Edita «Rareza», «Coste</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>&gt; «Coste nuevo», «A», «D», «V», «Rasgo» y «Texto del rasgo»**: el id es la</t>
+          <t>&gt; nuevo», «A», «D», «V», «Rasgo» y «Texto del rasgo»**: el id es la llave, y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>&gt; llave y las demás columnas se ignoran al aplicar.</t>
+          <t>&gt; «Carta», «Familia» y «Coste actual» son de referencia y se ignoran.</t>
         </is>
       </c>
     </row>
@@ -2180,274 +2179,233 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>&gt; - `node tools/tabla.mjs escribir` regenera esta tabla desde el código.</t>
+          <t>&gt; Cambiar la rareza mueve tres cosas a la vez: cuántas copias caben en un mazo,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>&gt; - `node tools/tabla.mjs aplicar` mete lo editado en `src/data/cards.js`.</t>
+          <t>&gt; cada cuánto sale la carta en un sobre y lo que da al fundirla. Si el mazo de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>&gt; referencia deja de ser legal, `aplicar` lo dice y no escribe nada.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>&gt; Si prefieres editarla en una hoja de cálculo, `python tools/excel.py escribir`</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>&gt; la saca a `RECOSTE.xlsx` y `python tools/excel.py leer` la trae de vuelta aquí.</t>
+          <t>&gt; - `node tools/tabla.mjs escribir` regenera esta tabla desde el código.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>&gt; - `node tools/tabla.mjs aplicar` mete lo editado en `src/data/cards.js`.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>&gt; Después de aplicar hay que correr `npm test` y `npm run sim`: los números</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>&gt; del balance salen de aquí.</t>
+          <t>&gt; Si prefieres editarla en una hoja de cálculo, `python tools/excel.py escribir`</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>&gt; la saca a `RECOSTE.xlsx` y `python tools/excel.py leer` la trae de vuelta aquí.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>## Por qué se recostea</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>&gt; Después de aplicar hay que correr `npm test` y `npm run sim`: los números</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Con la renta actual —la Biomasa vale el número de turno y no se acumula— cada</t>
+          <t>&gt; del balance salen de aquí.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>bando gasta **47 de Biomasa en 14,7 cartas** por partida, a un coste medio de</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3,22. Si la renta pasa a **+1 acumulativo**, el presupuesto de la partida entera</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>## Qué es esta tabla</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>baja a **11**: cuatro veces menos. Por eso la columna «Coste nuevo» arranca con</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>la escala 0–8 comprimida a **0–3**, que es la única que cabe en ese presupuesto.</t>
+          <t>Es un espejo del set: lo que hay en `src/data/cards.js` ahora mismo. «Coste</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>nuevo» arranca igual que «Coste actual» y lo que escribas ahí es lo que se</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>La propuesta de partida es mecánica (0-1→0, 2-3→1, 4-6→2, 7-8→3). Lo que hay que</t>
+          <t>aplica.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>revisar a mano es lo que una regla no sabe: qué carta merece costar más que otra</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>del mismo tramo.</t>
+          <t>La renta es de **1 de Biomasa por turno acumulativa**, con un tope de</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>12 de ahorro. Eso da un presupuesto de unas doce Biomasas por</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>## Qué mide la propuesta mecánica</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>partida de once turnos, que es la escala que tienen que respetar los costes: hoy</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>van de 0 a 3 y el gasto medido es de 12,1 en 10,8 cartas por bando.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Aplicada tal cual, con la renta acumulativa de +1, sobre 800 partidas:</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Cambiar la **rareza** mueve tres cosas a la vez: cuántas copias caben en un mazo</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>| Métrica | Hoy | Recoste 0–3 + renta +1 | Objetivo |</t>
+          <t>(3 común y rara, 2 épica, 1 legendaria), cada cuánto sale la carta en un sobre</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>—las probabilidades salen de la forma del set, así que mover una carta reajusta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>| Duración | 11,0 turnos | **9,6** | 10 – 14 |</t>
+          <t>la tabla entera— y lo que da al fundirla.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>| Victorias del inicial | 52,9 % | 49,0 % | 48 – 55 % |</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>| Bola de nieve | 61,5 % | 66,7 % | 55 – 70 % |</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>## Lo que hay que mirar después</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>| Reparto trofeos/hábitat/extinción | 36/40/24 | **4 / 74 / 22** | cada una 15 – 60 % |</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>| Cartas descalibradas | 1 de 25 | **14 de 25** | 0 |</t>
+          <t>Al aplicar, `aplicar` comprueba que el mazo de referencia siga siendo legal y</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>| Cartas jugadas por bando | 14,7 | 10,8 | — |</t>
+          <t>que no se quede ninguna rareza vacía; si algo falla no escribe nada. Después hay</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>que correr `npm test` y `npm run sim`: los seis objetivos del balance salen de</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Tres objetivos fuera, y la causa es la misma en los tres: con un presupuesto de</t>
+          <t>estos números, y el que hoy falla —cartas descalibradas— es justo el que esta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>doce Biomasas el campo se queda más vacío (1,86 unidades vivas por bando frente</t>
+          <t>revisión viene a arreglar.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>a 2,24), así que **el hábitat cae antes de que dé tiempo a reunir ocho trofeos**</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>y el registro fósil casi desaparece como vía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Eso no se arregla sólo con los costes: hay que mover también **trofeos para</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ganar** y **vida del hábitat**, que son los dos números que fijan cuánto dura la</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>partida. Esa calibración va después de esta revisión, con el simulador, y es</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>trabajo mío: aquí sólo hacen falta los costes que tú consideres justos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>Puede cambiar de ranura en vez de desplegar. Inmune a Sequía estacional.</t>
+          <t>Puede cambiar de ranura en vez de desplegar.</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>Agua permanente: la Sequía estacional no mata a nadie.</t>
+          <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
         </is>
       </c>
     </row>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,7 +112,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,7 +124,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -650,12 +653,12 @@
       <c r="J6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>+1 Poder por cada otro Dryosaurus propio en el campo.</t>
         </is>
@@ -701,12 +704,12 @@
       <c r="J7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Oportunista</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
         </is>
@@ -752,12 +755,12 @@
       <c r="J8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>+2 Poder mientras el campo activo sea Canal fluvial trenzado.</t>
         </is>
@@ -803,12 +806,12 @@
       <c r="J9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Tagomizador</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Devuelve 2 de daño adicional a quien lo ataque, además del que ya devuelve su clado.</t>
         </is>
@@ -854,12 +857,12 @@
       <c r="J10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Depredador dominante</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Si mata a su rival, el daño sobrante pasa al hábitat enemigo.</t>
         </is>
@@ -905,12 +908,12 @@
       <c r="J11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Migrador</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Puede cambiar de ranura en vez de desplegar.</t>
         </is>
@@ -956,12 +959,12 @@
       <c r="J12" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Ramoneo bajo</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Cura 1 herida al final de cada turno.</t>
         </is>
@@ -1007,12 +1010,12 @@
       <c r="J13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Masa colosal</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>+1 de Defensa adicional: es la mayor masa del set.</t>
         </is>
@@ -1058,12 +1061,12 @@
       <c r="J14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Escaso</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Sólo 1 copia en el mazo. No admite adaptaciones.</t>
         </is>
@@ -1109,12 +1112,12 @@
       <c r="J15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Coraza dorsal</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>+2 de Defensa. La coraza protege; no es un arma, a diferencia de la cola del estegosaurio.</t>
         </is>
@@ -1160,12 +1163,12 @@
       <c r="J16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>+2 Poder mientras el Canal fluvial esté en el campo.</t>
         </is>
@@ -1211,12 +1214,12 @@
       <c r="J17" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Gola ornamentada</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>+2 de Defensa.</t>
         </is>
@@ -1262,12 +1265,12 @@
       <c r="J18" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>+1 Poder por cada copia suya que tengas en el campo.</t>
         </is>
@@ -1313,12 +1316,12 @@
       <c r="J19" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>Desgarro</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>A quien hiere no se le cura ninguna herida ese turno.</t>
         </is>
@@ -1364,12 +1367,12 @@
       <c r="J20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>Sobrevuela la ranura: golpea siempre al hábitat rival y no recibe daño de combate.</t>
         </is>
@@ -1409,12 +1412,12 @@
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>+2 Poder a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
@@ -1454,12 +1457,12 @@
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>El objetivo cura 1 herida al final de cada turno.</t>
         </is>
@@ -1499,12 +1502,12 @@
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>+2 Poder y +2 Vida permanentes.</t>
         </is>
@@ -1544,12 +1547,12 @@
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>+2 Poder. Sólo sobre terópodos y saurópodos.</t>
         </is>
@@ -1589,12 +1592,12 @@
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
@@ -1634,12 +1637,12 @@
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>−2 Poder a todos los dinosaurios rivales del clado que elijas.</t>
         </is>
@@ -1679,12 +1682,12 @@
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>El rival pierde 12 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
@@ -1724,12 +1727,12 @@
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>2 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
@@ -1769,12 +1772,12 @@
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>+3 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
@@ -1814,12 +1817,12 @@
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
@@ -1859,12 +1862,12 @@
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Tu hábitat pierde 1.</t>
         </is>
@@ -1904,12 +1907,12 @@
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>+1 Biomasa por turno a los dos bandos.</t>
         </is>
@@ -1949,12 +1952,12 @@
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
         </is>
@@ -1994,12 +1997,12 @@
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
@@ -2039,12 +2042,12 @@
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>Cada turno, los dos bandos pierden 5 cartas del mazo.</t>
         </is>
@@ -2084,12 +2087,12 @@
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>Terreno abierto, sin cobertura: +1 al daño contra los biomas.</t>
         </is>
@@ -2139,7 +2142,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t># RECOSTE.md — la tabla editable del set</t>
         </is>
@@ -2264,7 +2267,7 @@
       <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>## Qué es esta tabla</t>
         </is>
@@ -2360,7 +2363,7 @@
       <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>## Lo que hay que mirar después</t>
         </is>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,8 @@
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="78" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,14 +541,14 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edita las columnas amarillas: Rareza, Coste nuevo, A, D, V, Rasgo y Texto del rasgo. La rareza se elige del desplegable; los costes son enteros de 0 a 8 (ej. 2) y A, D y V van de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran al aplicar.</t>
+          <t>Edita las columnas amarillas. La rareza se elige del desplegable; los costes son enteros de 0 a 8 (ej. 2) y A, D y V van de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran al aplicar.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>No cambies el id, no borres ni añadas filas y no reordenes: el id es la llave con la que cada fila vuelve a su carta. Los eventos, climas y recursos no tienen A/D/V y se quedan en blanco. Cambiar la rareza mueve las copias que caben en un mazo, lo que sale en los sobres y la fusión.</t>
+          <t>«Texto del rasgo» es lo que la carta DICE: sirve para redactar mejor una regla que ya existe. Para pedir una regla DISTINTA, descríbela en «Mecánica nueva» — eso hay que escribirlo en el motor, no lo aplica la herramienta. No cambies el id ni reordenes filas: el id es la llave.</t>
         </is>
       </c>
     </row>
@@ -612,6 +613,11 @@
           <t>Texto del rasgo</t>
         </is>
       </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Mecánica nueva</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -663,6 +669,7 @@
           <t>+1 Poder por cada otro Dryosaurus propio en el campo.</t>
         </is>
       </c>
+      <c r="M6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -714,6 +721,7 @@
           <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
         </is>
       </c>
+      <c r="M7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -765,6 +773,7 @@
           <t>+2 Poder mientras el campo activo sea Canal fluvial trenzado.</t>
         </is>
       </c>
+      <c r="M8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -816,6 +825,7 @@
           <t>Devuelve 2 de daño adicional a quien lo ataque, además del que ya devuelve su clado.</t>
         </is>
       </c>
+      <c r="M9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -867,6 +877,7 @@
           <t>Si mata a su rival, el daño sobrante pasa al hábitat enemigo.</t>
         </is>
       </c>
+      <c r="M10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -918,6 +929,7 @@
           <t>Puede cambiar de ranura en vez de desplegar.</t>
         </is>
       </c>
+      <c r="M11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -969,6 +981,7 @@
           <t>Cura 1 herida al final de cada turno.</t>
         </is>
       </c>
+      <c r="M12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1020,6 +1033,7 @@
           <t>+1 de Defensa adicional: es la mayor masa del set.</t>
         </is>
       </c>
+      <c r="M13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1071,6 +1085,7 @@
           <t>Sólo 1 copia en el mazo. No admite adaptaciones.</t>
         </is>
       </c>
+      <c r="M14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1122,6 +1137,7 @@
           <t>+2 de Defensa. La coraza protege; no es un arma, a diferencia de la cola del estegosaurio.</t>
         </is>
       </c>
+      <c r="M15" s="9" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1173,6 +1189,7 @@
           <t>+2 Poder mientras el Canal fluvial esté en el campo.</t>
         </is>
       </c>
+      <c r="M16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1224,6 +1241,7 @@
           <t>+2 de Defensa.</t>
         </is>
       </c>
+      <c r="M17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1275,6 +1293,7 @@
           <t>+1 Poder por cada copia suya que tengas en el campo.</t>
         </is>
       </c>
+      <c r="M18" s="9" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1326,6 +1345,7 @@
           <t>A quien hiere no se le cura ninguna herida ese turno.</t>
         </is>
       </c>
+      <c r="M19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1377,6 +1397,7 @@
           <t>Sobrevuela la ranura: golpea siempre al hábitat rival y no recibe daño de combate.</t>
         </is>
       </c>
+      <c r="M20" s="9" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1422,6 +1443,7 @@
           <t>+2 Poder a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
+      <c r="M21" s="9" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1467,6 +1489,7 @@
           <t>El objetivo cura 1 herida al final de cada turno.</t>
         </is>
       </c>
+      <c r="M22" s="9" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1512,6 +1535,7 @@
           <t>+2 Poder y +2 Vida permanentes.</t>
         </is>
       </c>
+      <c r="M23" s="9" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1557,6 +1581,7 @@
           <t>+2 Poder. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
+      <c r="M24" s="9" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1602,6 +1627,7 @@
           <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
+      <c r="M25" s="9" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1647,6 +1673,7 @@
           <t>−2 Poder a todos los dinosaurios rivales del clado que elijas.</t>
         </is>
       </c>
+      <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1692,6 +1719,7 @@
           <t>El rival pierde 12 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
+      <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1737,6 +1765,7 @@
           <t>2 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
+      <c r="M28" s="9" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1782,6 +1811,7 @@
           <t>+3 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
+      <c r="M29" s="9" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1827,6 +1857,7 @@
           <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
       </c>
+      <c r="M30" s="9" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1872,6 +1903,7 @@
           <t>+2 Biomasa ahora mismo. Tu hábitat pierde 1.</t>
         </is>
       </c>
+      <c r="M31" s="9" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1917,6 +1949,7 @@
           <t>+1 Biomasa por turno a los dos bandos.</t>
         </is>
       </c>
+      <c r="M32" s="9" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1962,6 +1995,7 @@
           <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
         </is>
       </c>
+      <c r="M33" s="9" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2007,6 +2041,7 @@
           <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
+      <c r="M34" s="9" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2052,6 +2087,7 @@
           <t>Cada turno, los dos bandos pierden 5 cartas del mazo.</t>
         </is>
       </c>
+      <c r="M35" s="9" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2097,6 +2133,7 @@
           <t>Terreno abierto, sin cobertura: +1 al daño contra los biomas.</t>
         </is>
       </c>
+      <c r="M36" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:L36"/>
@@ -2128,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2303,112 +2340,181 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>La renta es de **1 de Biomasa por turno acumulativa**, con un tope de</t>
+          <t>**«Texto del rasgo» es lo que la carta DICE, no lo que HACE.** Lo que hace sale</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>12 de ahorro. Eso da un presupuesto de unas doce Biomasas por</t>
+          <t>de una constante del código sobre la que el motor decide en sesenta sitios; el</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>partida de once turnos, que es la escala que tienen que respetar los costes: hoy</t>
+          <t>texto sólo se pinta. Así que editarlo sirve para redactar mejor una regla que</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>van de 0 a 3 y el gasto medido es de 12,1 en 10,8 cartas por bando.</t>
+          <t>ya existe, y si se le escribe una regla distinta la carta seguirá haciendo lo</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>de antes y el texto mentirá.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Cambiar la **rareza** mueve tres cosas a la vez: cuántas copias caben en un mazo</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>(3 común y rara, 2 épica, 1 legendaria), cada cuánto sale la carta en un sobre</t>
+          <t>Para pedir una regla distinta está **«Mecánica nueva»**: se escribe ahí, en</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>—las probabilidades salen de la forma del set, así que mover una carta reajusta</t>
+          <t>lenguaje llano, qué debería hacer la carta. Esa columna no la aplica ninguna</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>la tabla entera— y lo que da al fundirla.</t>
+          <t>herramienta —hay que escribirla en el motor y medirla—, pero `aplicar` la lee</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>y la lista al terminar para que no se quede olvidada.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>## Lo que hay que mirar después</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>La renta es de **1 de Biomasa por turno acumulativa**, con un tope de</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Al aplicar, `aplicar` comprueba que el mazo de referencia siga siendo legal y</t>
+          <t>12 de ahorro. Eso da un presupuesto de unas doce Biomasas por</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>que no se quede ninguna rareza vacía; si algo falla no escribe nada. Después hay</t>
+          <t>partida de once turnos, que es la escala que tienen que respetar los costes: hoy</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>que correr `npm test` y `npm run sim`: los seis objetivos del balance salen de</t>
+          <t>van de 0 a 3 y el gasto medido es de 12,1 en 10,8 cartas por bando.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>estos números, y el que hoy falla —cartas descalibradas— es justo el que esta</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>Cambiar la **rareza** mueve tres cosas a la vez: cuántas copias caben en un mazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>(3 común y rara, 2 épica, 1 legendaria), cada cuánto sale la carta en un sobre</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>—las probabilidades salen de la forma del set, así que mover una carta reajusta</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>la tabla entera— y lo que da al fundirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>## Lo que hay que mirar después</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Al aplicar, `aplicar` comprueba que el mazo de referencia siga siendo legal y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>que no se quede ninguna rareza vacía; si algo falla no escribe nada. Después hay</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>que correr `npm test` y `npm run sim`: los seis objetivos del balance salen de</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>estos números, y el que hoy falla —cartas descalibradas— es justo el que esta</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>revisión viene a arreglar.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>+1 Poder por cada otro Dryosaurus propio en el campo.</t>
+          <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr"/>
@@ -703,13 +703,13 @@
         <v/>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
@@ -755,10 +755,10 @@
         <v/>
       </c>
       <c r="H8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>3</v>
@@ -793,7 +793,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
@@ -807,13 +807,13 @@
         <v/>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
@@ -845,27 +845,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="6">
         <f>IF(F10="","",F10-E10)</f>
         <v/>
       </c>
       <c r="H10" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="6">
         <f>IF(F11="","",F11-E11)</f>
         <v/>
       </c>
       <c r="H11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="J11" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
@@ -966,7 +966,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Cura 1 herida al final de cada turno.</t>
+          <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -1015,13 +1015,13 @@
         <v/>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
@@ -1057,23 +1057,23 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="6">
         <f>IF(F14="","",F14-E14)</f>
         <v/>
       </c>
       <c r="H14" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         <v/>
       </c>
       <c r="H16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>+2 Poder mientras el Canal fluvial esté en el campo.</t>
+          <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="6">
         <f>IF(F17="","",F17-E17)</f>
@@ -1226,7 +1226,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
@@ -1275,7 +1275,7 @@
         <v/>
       </c>
       <c r="H18" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
@@ -1317,23 +1317,23 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="6">
         <f>IF(F19="","",F19-E19)</f>
         <v/>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
@@ -1379,13 +1379,13 @@
         <v/>
       </c>
       <c r="H20" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>+2 Poder a todos tus dinosaurios de la misma especie que el objetivo.</t>
+          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>El objetivo cura 1 herida al final de cada turno.</t>
+          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>+2 Poder y +2 Vida permanentes.</t>
+          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6">
         <f>IF(F25="","",F25-E25)</f>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" s="6">
         <f>IF(F26="","",F26-E26)</f>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>El rival pierde 12 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
+          <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>2 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
+          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 1.</t>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>+1 Biomasa por turno a los dos bandos.</t>
+          <t>+1 Biomasa para ambos jugadores</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>Cada turno, los dos bandos pierden 5 cartas del mazo.</t>
+          <t>Ambos jugadores pierden 5 cartas del mazo</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -765,12 +765,12 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Ribereño</t>
+          <t>Caza en grupo</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>+2 Poder mientras el campo activo sea Canal fluvial trenzado.</t>
+          <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr"/>
@@ -817,12 +817,12 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Tagomizador</t>
+          <t>Muro de placas</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Devuelve 2 de daño adicional a quien lo ataque, además del que ya devuelve su clado.</t>
+          <t>+1 de Defensa si tienes otro Stegosaurus en el campo.</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Puede cambiar de ranura en vez de desplegar.</t>
+          <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr"/>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Masa colosal</t>
+          <t>Manada</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>+1 de Defensa adicional: es la mayor masa del set.</t>
+          <t>+1 de Defensa si tienes otro saurópodo en el campo.</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr"/>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Escaso</t>
+          <t>Rastreador</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Sólo 1 copia en el mazo. No admite adaptaciones.</t>
+          <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
       <c r="M14" s="9" t="inlineStr"/>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Coraza dorsal</t>
+          <t>Llamada de manada</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>+2 de Defensa. La coraza protege; no es un arma, a diferencia de la cola del estegosaurio.</t>
+          <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>+2 de Defensa.</t>
+          <t>+2 de Defensa si tienes otro Lokiceratops en el campo.</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Sobrevuela la ranura: golpea siempre al hábitat rival y no recibe daño de combate.</t>
+          <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="6">
         <f>IF(F24="","",F24-E24)</f>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>+2 Poder. Sólo sobre terópodos y saurópodos.</t>
+          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>−2 Poder a todos los dinosaurios rivales del clado que elijas.</t>
+          <t>−2 de Defensa a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cartas'!$A$5:$L$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cartas'!$A$5:$L$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2135,22 +2135,1894 @@
       </c>
       <c r="M36" s="9" t="inlineStr"/>
     </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>plesiopleurodon</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Plesiopleurodon wellesi</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Reptil marino</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6">
+        <f>IF(F37="","",F37-E37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ojoraptorsaurus</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Ojoraptorsaurus boerei</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="6">
+        <f>IF(F38="","",F38-E38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>dromaeosaurus</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Dromaeosaurus albertensis</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="6">
+        <f>IF(F39="","",F39-E39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>athenar</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Athenar</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6">
+        <f>IF(F40="","",F40-E40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>sanjuansaurus</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Sanjuansaurus gordilloi</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="6">
+        <f>IF(F41="","",F41-E41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>suchomimus</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Suchomimus tenerensis</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="6">
+        <f>IF(F42="","",F42-E42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>eosinopteryx</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Eosinopteryx brevipenna</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="6">
+        <f>IF(F43="","",F43-E43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>troodon</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Troodon formosus</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="6">
+        <f>IF(F44="","",F44-E44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>carnotaurus</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Carnotaurus sastrei</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
+        <f>IF(F45="","",F45-E45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>spinosaurus</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Spinosaurus aegyptiacus</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="6">
+        <f>IF(F46="","",F46-E46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>mosasaurus</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Mosasaurus hoffmannii</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Reptil marino</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
+        <f>IF(F47="","",F47-E47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>halszkaraptor</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Halszkaraptor escuilliei</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="6">
+        <f>IF(F48="","",F48-E48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>tongtianlong</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Tongtianlong limosus</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="6">
+        <f>IF(F49="","",F49-E49)</f>
+        <v/>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>scanisaurus</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Scanisaurus nazarowi</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Reptil marino</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="6">
+        <f>IF(F50="","",F50-E50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>monolophosaurus</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Monolophosaurus jiangi</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="6">
+        <f>IF(F51="","",F51-E51)</f>
+        <v/>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>invictarx</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Invictarx zephyri</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="6">
+        <f>IF(F52="","",F52-E52)</f>
+        <v/>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>medusaceratops</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Medusaceratops lokii</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="6">
+        <f>IF(F53="","",F53-E53)</f>
+        <v/>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>platyceratops</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Platyceratops tatarinovi</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="6">
+        <f>IF(F54="","",F54-E54)</f>
+        <v/>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>loricatosaurus</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Loricatosaurus priscus</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="6">
+        <f>IF(F55="","",F55-E55)</f>
+        <v/>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>therizinosaurus</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Therizinosaurus cheloniformis</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="6">
+        <f>IF(F56="","",F56-E56)</f>
+        <v/>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>alaskacephale</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Alaskacephale gangloffi</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6">
+        <f>IF(F57="","",F57-E57)</f>
+        <v/>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>titanoceratops</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Titanoceratops ouranos</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="6">
+        <f>IF(F58="","",F58-E58)</f>
+        <v/>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>atlasaurus</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Atlasaurus imelakei</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="6">
+        <f>IF(F59="","",F59-E59)</f>
+        <v/>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>stegoceras</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Stegoceras validum</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="6">
+        <f>IF(F60="","",F60-E60)</f>
+        <v/>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>maiasaura</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Maiasaura peeblesorum</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="6">
+        <f>IF(F61="","",F61-E61)</f>
+        <v/>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>edmontosaurus</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Edmontosaurus annectens</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="6">
+        <f>IF(F62="","",F62-E62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>plateosauravus</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Plateosauravus cullingworthi</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6">
+        <f>IF(F63="","",F63-E63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>gargoyleosaurus</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Gargoyleosaurus parkpinorum</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="6">
+        <f>IF(F64="","",F64-E64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>wendiceratops</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Wendiceratops pinhornensis</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="6">
+        <f>IF(F65="","",F65-E65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>domeykosaurus</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Domeykosaurus chilensis</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6">
+        <f>IF(F66="","",F66-E66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>antarctosaurus</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Antarctosaurus wichmannianus</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6">
+        <f>IF(F67="","",F67-E67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>liaoceratops</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Liaoceratops yanzigouensis</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="6">
+        <f>IF(F68="","",F68-E68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>rhinorex</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Rhinorex condrupus</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="6">
+        <f>IF(F69="","",F69-E69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>bienosaurus</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Bienosaurus lufengensis</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="6">
+        <f>IF(F70="","",F70-E70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>shuangmiaosaurus</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Shuangmiaosaurus gilmorei</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="6">
+        <f>IF(F71="","",F71-E71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>chasmosaurus</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Chasmosaurus belli</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="6">
+        <f>IF(F72="","",F72-E72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>Sin rasgo</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>Todavía no hace nada especial.</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:L36"/>
+  <autoFilter ref="A5:L72"/>
   <mergeCells count="2">
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="F6:F36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
+    <dataValidation sqref="F6:F72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
-    <dataValidation sqref="H6:J36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque, Defensa y Vida van de 0 a 20." type="whole" operator="between">
+    <dataValidation sqref="H6:J72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque, Defensa y Vida van de 0 a 20." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="D6:D36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
+    <dataValidation sqref="D6:D72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
       <formula1>"Común,Rara,Épica,Legendaria"</formula1>
     </dataValidation>
   </dataValidations>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cartas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mecánicas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clados" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mazo de referencia" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cartas'!$A$5:$L$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cartas'!$A$5:$K$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,6 +132,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -513,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -525,10 +532,9 @@
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,7 +547,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edita las columnas amarillas. La rareza se elige del desplegable; los costes son enteros de 0 a 8 (ej. 2) y A, D y V van de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran al aplicar.</t>
+          <t>Edita las columnas amarillas. La rareza se elige del desplegable; los costes son enteros de 0 a 8 (ej. 2) y A y V van de 0 a 20 (ej. 6). Las columnas grises son de referencia y se ignoran al aplicar.</t>
         </is>
       </c>
     </row>
@@ -595,25 +601,20 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Rasgo</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Rasgo</t>
+          <t>Texto del rasgo</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Texto del rasgo</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Mecánica nueva</t>
         </is>
@@ -654,22 +655,19 @@
         <v>1</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -703,25 +701,22 @@
         <v/>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Oportunista</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -758,22 +753,19 @@
         <v>3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Caza en grupo</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -810,22 +802,19 @@
         <v>1</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Muro de placas</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>+1 de Defensa si tienes otro Stegosaurus en el campo.</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -862,22 +851,19 @@
         <v>5</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Depredador dominante</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>Si mata a su rival, el daño sobrante pasa al hábitat enemigo.</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -914,22 +900,19 @@
         <v>2</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Migrador</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -966,22 +949,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Ramoneo bajo</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1018,22 +998,19 @@
         <v>2</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Manada</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>+1 de Defensa si tienes otro saurópodo en el campo.</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1070,22 +1047,19 @@
         <v>7</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Rastreador</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1122,22 +1096,19 @@
         <v>2</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Llamada de manada</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1174,22 +1145,19 @@
         <v>4</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1226,22 +1194,19 @@
         <v>4</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Gola ornamentada</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>+2 de Defensa si tienes otro Lokiceratops en el campo.</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1278,22 +1243,19 @@
         <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>+1 Poder por cada copia suya que tengas en el campo.</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1330,22 +1292,19 @@
         <v>10</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Desgarro</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>A quien hiere no se le cura ninguna herida ese turno.</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1382,22 +1341,19 @@
         <v>2</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1432,18 +1388,17 @@
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1478,18 +1433,17 @@
       </c>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1524,18 +1478,17 @@
       </c>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1570,18 +1523,17 @@
       </c>
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1616,18 +1568,17 @@
       </c>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1662,18 +1613,17 @@
       </c>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>−2 de Defensa a dos dinosaurios rivales que elijas.</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1708,18 +1658,17 @@
       </c>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1754,18 +1703,17 @@
       </c>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1800,18 +1748,17 @@
       </c>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="L29" s="9" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1846,18 +1793,17 @@
       </c>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1892,18 +1838,17 @@
       </c>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1938,18 +1883,17 @@
       </c>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>+1 Biomasa para ambos jugadores</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Mientras esté en el campo, cada jugador puede devolver una carta de su mano al fondo de su mazo, una vez por turno.</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1984,18 +1928,17 @@
       </c>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -2030,18 +1973,17 @@
       </c>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -2076,18 +2018,17 @@
       </c>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>Ambos jugadores pierden 5 cartas del mazo</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -2122,18 +2063,17 @@
       </c>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>Terreno abierto, sin cobertura: +1 al daño contra los biomas.</t>
-        </is>
-      </c>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2153,39 +2093,36 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="6">
         <f>IF(F37="","",F37-E37)</f>
         <v/>
       </c>
       <c r="H37" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2205,39 +2142,36 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="6">
         <f>IF(F38="","",F38-E38)</f>
         <v/>
       </c>
       <c r="H38" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="L38" s="9" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2261,35 +2195,32 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6">
         <f>IF(F39="","",F39-E39)</f>
         <v/>
       </c>
       <c r="H39" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2299,12 +2230,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Athenar</t>
+          <t>Athenar bermani</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Terópodo</t>
+          <t>Saurópodo</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2313,35 +2244,32 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="6">
         <f>IF(F40="","",F40-E40)</f>
         <v/>
       </c>
       <c r="H40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2361,39 +2289,36 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6">
         <f>IF(F41="","",F41-E41)</f>
         <v/>
       </c>
       <c r="H41" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2413,39 +2338,36 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="6">
         <f>IF(F42="","",F42-E42)</f>
         <v/>
       </c>
       <c r="H42" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2479,25 +2401,22 @@
         <v/>
       </c>
       <c r="H43" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2521,35 +2440,32 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="6">
         <f>IF(F44="","",F44-E44)</f>
         <v/>
       </c>
       <c r="H44" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -2569,39 +2485,36 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" s="6">
         <f>IF(F45="","",F45-E45)</f>
         <v/>
       </c>
       <c r="H45" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr"/>
+      <c r="L45" s="9" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -2621,39 +2534,36 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46" s="6">
         <f>IF(F46="","",F46-E46)</f>
         <v/>
       </c>
       <c r="H46" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="K46" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M46" s="9" t="inlineStr"/>
+      <c r="L46" s="9" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -2673,39 +2583,36 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G47" s="6">
         <f>IF(F47="","",F47-E47)</f>
         <v/>
       </c>
       <c r="H47" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -2739,25 +2646,22 @@
         <v/>
       </c>
       <c r="H48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="K48" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M48" s="9" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -2794,22 +2698,19 @@
         <v>1</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr">
+      <c r="K49" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -2829,39 +2730,36 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" s="6">
         <f>IF(F50="","",F50-E50)</f>
         <v/>
       </c>
       <c r="H50" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -2881,39 +2779,36 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="6">
         <f>IF(F51="","",F51-E51)</f>
         <v/>
       </c>
       <c r="H51" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr">
+      <c r="K51" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -2933,39 +2828,36 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="6">
         <f>IF(F52="","",F52-E52)</f>
         <v/>
       </c>
       <c r="H52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L52" s="9" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M52" s="9" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -2985,39 +2877,36 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" s="6">
         <f>IF(F53="","",F53-E53)</f>
         <v/>
       </c>
       <c r="H53" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L53" s="9" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -3054,22 +2943,19 @@
         <v>1</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -3089,39 +2975,36 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" s="6">
         <f>IF(F55="","",F55-E55)</f>
         <v/>
       </c>
       <c r="H55" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L55" s="9" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr"/>
+      <c r="L55" s="9" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -3141,39 +3024,36 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56" s="6">
         <f>IF(F56="","",F56-E56)</f>
         <v/>
       </c>
       <c r="H56" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M56" s="9" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -3193,39 +3073,36 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6">
         <f>IF(F57="","",F57-E57)</f>
         <v/>
       </c>
       <c r="H57" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
+      <c r="K57" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -3245,39 +3122,36 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" s="6">
         <f>IF(F58="","",F58-E58)</f>
         <v/>
       </c>
       <c r="H58" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
+      <c r="K58" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -3297,39 +3171,36 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" s="6">
         <f>IF(F59="","",F59-E59)</f>
         <v/>
       </c>
       <c r="H59" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="8" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -3353,35 +3224,32 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="6">
         <f>IF(F60="","",F60-E60)</f>
         <v/>
       </c>
       <c r="H60" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr">
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M60" s="9" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -3401,39 +3269,36 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="6">
         <f>IF(F61="","",F61-E61)</f>
         <v/>
       </c>
       <c r="H61" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L61" s="9" t="inlineStr">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="L61" s="9" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -3453,39 +3318,36 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G62" s="6">
         <f>IF(F62="","",F62-E62)</f>
         <v/>
       </c>
       <c r="H62" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M62" s="9" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -3509,35 +3371,32 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="6">
         <f>IF(F63="","",F63-E63)</f>
         <v/>
       </c>
       <c r="H63" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr">
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M63" s="9" t="inlineStr"/>
+      <c r="L63" s="9" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -3557,39 +3416,36 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="6">
         <f>IF(F64="","",F64-E64)</f>
         <v/>
       </c>
       <c r="H64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L64" s="9" t="inlineStr">
+      <c r="K64" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M64" s="9" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -3609,49 +3465,46 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" s="6">
         <f>IF(F65="","",F65-E65)</f>
         <v/>
       </c>
       <c r="H65" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="8" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L65" s="9" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>domeykosaurus</t>
+          <t>antarctosaurus</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Domeykosaurus chilensis</t>
+          <t>Antarctosaurus wichmannianus</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3661,54 +3514,51 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66" s="6">
         <f>IF(F66="","",F66-E66)</f>
         <v/>
       </c>
       <c r="H66" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" s="8" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L66" s="9" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>antarctosaurus</t>
+          <t>liaoceratops</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Antarctosaurus wichmannianus</t>
+          <t>Liaoceratops yanzigouensis</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Saurópodo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3730,89 +3580,83 @@
         <v>1</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M67" s="9" t="inlineStr"/>
+      <c r="L67" s="9" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>liaoceratops</t>
+          <t>rhinorex</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Liaoceratops yanzigouensis</t>
+          <t>Rhinorex condrupus</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Marginocéfalo</t>
+          <t>Ornitópodo</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" s="6">
         <f>IF(F68="","",F68-E68)</f>
         <v/>
       </c>
       <c r="H68" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" s="8" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>rhinorex</t>
+          <t>bienosaurus</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Rhinorex condrupus</t>
+          <t>Bienosaurus lufengensis</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Ornitópodo</t>
+          <t>Tireóforo</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3834,37 +3678,34 @@
         <v>1</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>bienosaurus</t>
+          <t>shuangmiaosaurus</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Bienosaurus lufengensis</t>
+          <t>Shuangmiaosaurus gilmorei</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Tireóforo</t>
+          <t>Ornitópodo</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3873,50 +3714,47 @@
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="6">
         <f>IF(F70="","",F70-E70)</f>
         <v/>
       </c>
       <c r="H70" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="8" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>shuangmiaosaurus</t>
+          <t>chasmosaurus</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Shuangmiaosaurus gilmorei</t>
+          <t>Chasmosaurus belli</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Ornitópodo</t>
+          <t>Marginocéfalo</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3925,104 +3763,49 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="6">
         <f>IF(F71="","",F71-E71)</f>
         <v/>
       </c>
       <c r="H71" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" s="8" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="K71" s="9" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="M71" s="9" t="inlineStr"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>chasmosaurus</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Chasmosaurus belli</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Marginocéfalo</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Común</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="6">
-        <f>IF(F72="","",F72-E72)</f>
-        <v/>
-      </c>
-      <c r="H72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
-      <c r="M72" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L72"/>
+  <autoFilter ref="A5:K71"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="F6:F72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
+    <dataValidation sqref="F6:F71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coste fuera de rango" error="El coste es un número entero de 0 a 8." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
-    <dataValidation sqref="H6:J72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque, Defensa y Vida van de 0 a 20." type="whole" operator="between">
+    <dataValidation sqref="H6:I71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estadística fuera de rango" error="Ataque y Vida van de 0 a 20." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="D6:D72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
+    <dataValidation sqref="D6:D71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Rareza no válida" error="Elige una de: Común, Rara, Épica, Legendaria" type="list">
       <formula1>"Común,Rara,Épica,Legendaria"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4037,7 +3820,1988 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Qué hace cada rasgo, y cuánto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sale del código: el número es la constante de balance.js que mueve ese rasgo. Editar esta hoja no cambia nada — para pedir una regla distinta, usa la columna «Mecánica nueva» de la hoja Cartas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rasgo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cartas</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Quiénes lo llevan</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Lo que dice la carta</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Qué es ese número</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Constante</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Depredador dominante</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Allosaurus fragilis, Saurophaganax maximus</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Gregario</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Dryosaurus altus, Brachylophosaurus canadensis</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Ataque por cada congénere en el campo</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.gregarioAtaquePorCompanero</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Manada</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Apatosaurus louisae, Barosaurus lentus</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Vida con otro del mismo clado</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.manadaVida</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Bosque de coníferas ribereño</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Bosque de coníferas ribereño</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>heridas que curan los saurópodos</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>efectosCampo.bosqueCura</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Canal fluvial trenzado</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Canal fluvial trenzado</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Vida a todos los del campo</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>efectosCampo.canalVida</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Carroña abundante</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Carroña abundante</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Caza en grupo</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Ceratosaurus nasicornis</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Ataque si hay bastantes copias en el campo</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.cazaEnGrupoAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Competencia trófica</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Competencia trófica</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Vida que se quita, a dos rivales</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.competenciaVida</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Crecimiento acelerado</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Crecimiento acelerado</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Ataque, y otro tanto de Vida</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.crecimientoAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Deriva árida</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Deriva árida</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Ambos jugadores pierden 5 cartas del mazo</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>cartas de mazo que pierden los DOS</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>efectosCampo.aridezMazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Desgarro</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Tyrannotitan chubutensis</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>A quien hiere no se le cura ninguna herida ese turno.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Fractura consolidada</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Fractura consolidada</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>−2 Poder permanente a un dinosaurio rival.</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Ataque que se quita</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.fracturaAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Gastrolitos</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Gastrolitos</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>heridas curadas a un dinosaurio</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.gastrolitosCura</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Gola ornamentada</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Lokiceratops rangiformis</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Vida con otra copia en el campo</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.golaVida</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Gregarismo</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Gregarismo</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Ataque a toda la especie</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.gregarismoAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Lago efímero</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Lago efímero</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Llamada de manada</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Nodosaurus textilis</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Llanura de inundación</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Llanura de inundación</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en el campo, cada jugador puede devolver una carta de su mano al fondo de su mazo, una vez por turno.</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>cambio de carta por turno y jugador</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>efectosCampo.llanuraReciclaPorTurno</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Migrador</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Camarasaurus grandis</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Mortandad estacional</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Mortandad estacional</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>de daño a TODOS, incluidos los tuyos</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.mortandadDano</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Muro de placas</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Stegosaurus stenops</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Vida con otra copia en el campo</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.muroDePlacasVida</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Neumaticidad ósea</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Neumaticidad ósea</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Ataque permanente</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.neumaticidadAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Oportunista</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Ornitholestes hermanni</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Vida permanente por cada muerte</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.oportunistaVidaPorMuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Ramoneo bajo</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Diplodocus carnegii</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>heridas curadas al final del turno</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.ramoneoBajoCura</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Rastreador</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Torvosaurus tanneri</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Rebrote tras incendio</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Rebrote tras incendio</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ribereño</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Riparovenator milnerae</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Ataque con el Canal en el campo</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.riberenoAtaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Sabana de helechos</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Sabana de helechos</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Biomasa por turno a los DOS</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>efectosCampo.sabanaBiomasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Trampa de depredadores</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Trampa de depredadores</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>cartas que pierde el rival</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>rasgos.trampaMazoRival</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Vuelo</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Huaxiadraco corollatus</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Las reglas del tablero</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Contra esto se tasa una carta. Un coste no significa nada sin saber cuánta renta hay por turno ni cuánto aguanta un hábitat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Qué implica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Tablero</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Ranuras enfrentadas</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Cada una pelea contra la de enfrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Tablero</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Vida del hábitat</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Llegar a 0 pierde la partida</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Tablero</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Trofeos para ganar</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Cada baja rival es un trofeo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Tablero</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Límite de turnos</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Se decide por trofeos y luego por hábitat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Mano</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Mano inicial</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Se puede cambiar entera una vez (mulligan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Mano</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Mano máxima</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Por encima hay que descartar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Mazo</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Cartas del mazo</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Quedarse sin mazo pierde la partida</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Renta por turno</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Biomasa, plana, igual para los dos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Daño de un golpe</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>el Ataque</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Sin restas: no hay Defensa ni suelo de daño</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Bonus de depredación</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Terópodo contra ornitópodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Púas del tireóforo</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Se devuelven a quien le ataque</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Combate</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Daño sobrante</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>sí pasa</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Lo que sobra al matar sigue al hábitat rival</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Colección</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Precio del sobre</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>5 cartas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Colección</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Monedas por victoria</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Perder no paga nada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Colección</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Monedas de inicio</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Rareza</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Copias por mazo · comun</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Fundir una copia sobrante da 4 monedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Rareza</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Copias por mazo · raro</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Fundir una copia sobrante da 12 monedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Rareza</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Copias por mazo · epico</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Fundir una copia sobrante da 35 monedas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Rareza</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Copias por mazo · legendario</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Fundir una copia sobrante da 100 monedas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Los clados y la red trófica</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>No es piedra-papel-tijera. Sólo tres clados tienen regla propia; los demás se distinguen únicamente por sus cifras medias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Clado</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cartas</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ataque medio</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Vida media</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Regla propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Ornitópodo</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>es la presa del terópodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Terópodo</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>+2 de daño contra ornitópodos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Tireóforo</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>devuelve 2 de daño a quien le ataque</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Saurópodo</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>sin regla propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Marginocéfalo</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>sin regla propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Pterosaurio</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>sin regla propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Reptil marino</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>sin regla propia</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>El mazo que mide el simulador</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: `npm run sim` juega SÓLO este mazo. Una carta que no esté aquí no aparece en BALANCE.md por mucho que la cambies — para esas está `node sim/cobertura.mjs`, y para los climas `node sim/climas.js`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Copias en el mazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>dryosaurus</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ornitholestes</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ceratosaurus</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>nodosaurus</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>stegosaurus</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>allosaurus</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>camarasaurus</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>riparovenator</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>lokiceratops</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>brachylophosaurus</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>huaxiadraco</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>diplodocus</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>apatosaurus</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>torvosaurus</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>tyrannotitan</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>gregarismo</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>trampa</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>rebrote</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>gastrolitos</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>fractura</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>sabana</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>aridez</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>mortandad</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>crecimiento_acelerado</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>neumaticidad</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>competencia</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -4051,7 +5815,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t># RECOSTE.md — la tabla editable del set</t>
         </is>
@@ -4070,7 +5834,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>&gt; nuevo», «A», «D», «V», «Rasgo» y «Texto del rasgo»**: el id es la llave, y</t>
+          <t>&gt; nuevo», «A», «V», «Rasgo» y «Texto del rasgo»**: el id es la llave, y</t>
         </is>
       </c>
     </row>
@@ -4176,7 +5940,7 @@
       <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>## Qué es esta tabla</t>
         </is>
@@ -4281,28 +6045,28 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>La renta es de **1 de Biomasa por turno acumulativa**, con un tope de</t>
+          <t>La renta es de **2 de Biomasa por turno acumulativa**, con un</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12 de ahorro. Eso da un presupuesto de unas doce Biomasas por</t>
+          <t>tope de 12 de ahorro. En una partida de trece turnos eso son unas</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>partida de once turnos, que es la escala que tienen que respetar los costes: hoy</t>
+          <t>26 Biomasas para las once cartas que se llegan a desplegar, así que</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>van de 0 a 3 y el gasto medido es de 12,1 en 10,8 cartas por bando.</t>
+          <t>**el coste medio de una carta debería rondar el 2**, no el 1.</t>
         </is>
       </c>
     </row>
@@ -4312,38 +6076,42 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Cambiar la **rareza** mueve tres cosas a la vez: cuántas copias caben en un mazo</t>
+          <t>Y la curva tiene que ser más que proporcional. Robas una carta por turno y ganas</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>(3 común y rara, 2 épica, 1 legendaria), cada cuánto sale la carta en un sobre</t>
+          <t>2 de Biomasa, así que una carta de coste 4 te cuesta dos turnos de renta</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>—las probabilidades salen de la forma del set, así que mover una carta reajusta</t>
+          <t>**y** una de tus cinco ranuras, mientras que cuatro de coste 1 tapan cuatro</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>la tabla entera— y lo que da al fundirla.</t>
+          <t>carriles. Para que valga la pena, el cuerpo (A+D+V) tiene que crecer más deprisa</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>que el coste; la escala medida que funciona es del orden de **4 / 9 / 15 / 22**</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>## Lo que hay que mirar después</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>para costes de 1 a 4.</t>
         </is>
       </c>
     </row>
@@ -4353,40 +6121,119 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Al aplicar, `aplicar` comprueba que el mazo de referencia siga siendo legal y</t>
+          <t>Esto no es teoría: con renta 1 el índice de calibración era casi una función del</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>que no se quede ninguna rareza vacía; si algo falla no escribe nada. Después hay</t>
+          <t>coste —1,31 para el coste 0 y 0,10 para *Torvosaurus*, que costaba 4— y quince</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>que correr `npm test` y `npm run sim`: los seis objetivos del balance salen de</t>
+          <t>cartas se salían de banda. Subir el robo en vez de la renta lo empeoraba, lo que</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>estos números, y el que hoy falla —cartas descalibradas— es justo el que esta</t>
+          <t>confirma que el problema era la proporción entre cartas y Biomasa, no que</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>revisión viene a arreglar.</t>
+          <t>faltaran recursos.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Cambiar la **rareza** mueve tres cosas a la vez: cuántas copias caben en un mazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>(3 común y rara, 2 épica, 1 legendaria), cada cuánto sale la carta en un sobre</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>—las probabilidades salen de la forma del set, así que mover una carta reajusta</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>la tabla entera— y lo que da al fundirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>## Lo que hay que mirar después</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Al aplicar, `aplicar` comprueba que el mazo de referencia siga siendo legal y</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>que no se quede ninguna rareza vacía; si algo falla no escribe nada. Después hay</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>que correr `npm test` y `npm run sim`: los seis objetivos del balance salen de</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>estos números, y el que hoy falla —cartas descalibradas— es justo el que esta</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>revisión viene a arreglar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -1890,7 +1890,7 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede devolver una carta de su mano al fondo de su mazo, una vez por turno.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
+          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Agua permanente en el campo: los ribereños pelean a gusto.</t>
+          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede devolver una carta de su mano al fondo de su mazo, una vez por turno.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="E27" s="10" t="n">

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -7,15 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mecánicas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clados" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mazo de referencia" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mecánicas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mazo de referencia" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cartas'!$A$5:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,6 +117,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -132,9 +136,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -520,6 +521,273 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Contra qué estás recosteando</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sale de BALANCE.md, que escribe `npm run sim` sobre 2.000 partidas. Vuelve a correrlo después de aplicar cambios: `python tools/excel.py leer`, `node tools/tabla.mjs aplicar`, `npm test` y `npm run sim`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Duración media</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>11.03 turnos</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>10 – 14</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Victorias del jugador inicial</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>49.8 %</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>48 – 55 %</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Cartas mal calibradas</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>FALLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Partidas sin decisión</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0.0 %</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 2 %</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>P(ganar | ventaja en el turno 5)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>68.2 %</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>55 – 70 %</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reparto entre las tres victorias</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>36% / 44% / 19%</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>cada una 15 – 60 %</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cartas fuera de banda</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>índice 1,00 es la diana; fuera de 0,70–1,30 está mal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Competencia trófica</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>índice 0.00, uso 0 % (coste 3)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Canal fluvial trenzado</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>índice 0.32, uso 26 % (coste 1)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Torvosaurus tanneri</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>índice 0.70, uso 68 % (coste 4)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Gregarismo</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>índice 1.69, uso 95 % (coste 1)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -621,3174 +889,3174 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>dryosaurus</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Dryosaurus altus</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <f>IF(F6="","",F6-E6)</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ornitholestes</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Ornitholestes hermanni</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="E7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
         <f>IF(F7="","",F7-E7)</f>
         <v/>
       </c>
-      <c r="H7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Oportunista</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ceratosaurus</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Ceratosaurus nasicornis</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="E8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
         <f>IF(F8="","",F8-E8)</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Caza en grupo</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>stegosaurus</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Stegosaurus stenops</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="E9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7">
         <f>IF(F9="","",F9-E9)</f>
         <v/>
       </c>
-      <c r="H9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="7" t="n">
+      <c r="H9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Muro de placas</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>allosaurus</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Allosaurus fragilis</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <f>IF(F10="","",F10-E10)</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Depredador dominante</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>camarasaurus</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Camarasaurus grandis</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <f>IF(F11="","",F11-E11)</f>
         <v/>
       </c>
-      <c r="H11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="7" t="n">
+      <c r="H11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Migrador</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>diplodocus</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Diplodocus carnegii</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="E12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7">
         <f>IF(F12="","",F12-E12)</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Ramoneo bajo</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>apatosaurus</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Apatosaurus louisae</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="7">
         <f>IF(F13="","",F13-E13)</f>
         <v/>
       </c>
-      <c r="H13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="7" t="n">
+      <c r="H13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Manada</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>torvosaurus</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Torvosaurus tanneri</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="7">
         <f>IF(F14="","",F14-E14)</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Rastreador</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>nodosaurus</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Nodosaurus textilis</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="E15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="7">
         <f>IF(F15="","",F15-E15)</f>
         <v/>
       </c>
-      <c r="H15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="7" t="n">
+      <c r="H15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Llamada de manada</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>riparovenator</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Riparovenator milnerae</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="E16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="7">
         <f>IF(F16="","",F16-E16)</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr"/>
+      <c r="L16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>lokiceratops</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Lokiceratops rangiformis</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="7">
         <f>IF(F17="","",F17-E17)</f>
         <v/>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Gola ornamentada</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>brachylophosaurus</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Brachylophosaurus canadensis</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="E18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7">
         <f>IF(F18="","",F18-E18)</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="7" t="n">
+      <c r="H18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>+1 Poder por cada copia suya que tengas en el campo.</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr"/>
+      <c r="L18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>tyrannotitan</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Tyrannotitan chubutensis</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="7">
         <f>IF(F19="","",F19-E19)</f>
         <v/>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Desgarro</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>A quien hiere no se le cura ninguna herida ese turno.</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>huaxiadraco</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Huaxiadraco corollatus</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Pterosaurio</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="E20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7">
         <f>IF(F20="","",F20-E20)</f>
         <v/>
       </c>
-      <c r="H20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="7" t="n">
+      <c r="H20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>gregarismo</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="E21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7">
         <f>IF(F21="","",F21-E21)</f>
         <v/>
       </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>gastrolitos</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="E22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7">
         <f>IF(F22="","",F22-E22)</f>
         <v/>
       </c>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>crecimiento_acelerado</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="E23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7">
         <f>IF(F23="","",F23-E23)</f>
         <v/>
       </c>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>neumaticidad</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="E24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7">
         <f>IF(F24="","",F24-E24)</f>
         <v/>
       </c>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr"/>
+      <c r="L24" s="10" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>fractura</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="E25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="7">
         <f>IF(F25="","",F25-E25)</f>
         <v/>
       </c>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>competencia</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="7">
         <f>IF(F26="","",F26-E26)</f>
         <v/>
       </c>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr"/>
+      <c r="L26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>trampa</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="E27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7">
         <f>IF(F27="","",F27-E27)</f>
         <v/>
       </c>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>mortandad</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="E28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
         <f>IF(F28="","",F28-E28)</f>
         <v/>
       </c>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>rebrote</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="7">
         <f>IF(F29="","",F29-E29)</f>
         <v/>
       </c>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>carrona</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="7">
         <f>IF(F30="","",F30-E30)</f>
         <v/>
       </c>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
+      <c r="L30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>lago</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Recurso</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="7">
         <f>IF(F31="","",F31-E31)</f>
         <v/>
       </c>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>llanura</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Clima</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7">
         <f>IF(F32="","",F32-E32)</f>
         <v/>
       </c>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr"/>
+      <c r="L32" s="10" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Clima</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="E33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7">
         <f>IF(F33="","",F33-E33)</f>
         <v/>
       </c>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>bosque</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Clima</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="E34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7">
         <f>IF(F34="","",F34-E34)</f>
         <v/>
       </c>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr"/>
+      <c r="L34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>aridez</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Clima</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="E35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7">
         <f>IF(F35="","",F35-E35)</f>
         <v/>
       </c>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Ambos jugadores pierden 5 cartas del mazo</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr"/>
+      <c r="L35" s="10" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>sabana</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Clima</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="E36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7">
         <f>IF(F36="","",F36-E36)</f>
         <v/>
       </c>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>plesiopleurodon</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Plesiopleurodon wellesi</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Reptil marino</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="7">
         <f>IF(F37="","",F37-E37)</f>
         <v/>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="I37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ojoraptorsaurus</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Ojoraptorsaurus boerei</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="E38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="7">
         <f>IF(F38="","",F38-E38)</f>
         <v/>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr"/>
+      <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>dromaeosaurus</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Dromaeosaurus albertensis</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="6">
+      <c r="E39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="7">
         <f>IF(F39="","",F39-E39)</f>
         <v/>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, hace 3 de daño al dinosaurio que tenga enfrente.</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>athenar</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Athenar bermani</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="E40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="7">
         <f>IF(F40="","",F40-E40)</f>
         <v/>
       </c>
-      <c r="H40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="7" t="n">
+      <c r="H40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr"/>
+      <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>sanjuansaurus</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Sanjuansaurus gordilloi</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="E41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="7">
         <f>IF(F41="","",F41-E41)</f>
         <v/>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr"/>
+      <c r="L41" s="10" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>suchomimus</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Suchomimus tenerensis</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="7">
         <f>IF(F42="","",F42-E42)</f>
         <v/>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H42" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr"/>
+      <c r="L42" s="10" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>eosinopteryx</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Eosinopteryx brevipenna</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="6">
+      <c r="E43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="7">
         <f>IF(F43="","",F43-E43)</f>
         <v/>
       </c>
-      <c r="H43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>troodon</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Troodon formosus</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="E44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
         <f>IF(F44="","",F44-E44)</f>
         <v/>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, robas 1 carta.</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr"/>
+      <c r="L44" s="10" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>carnotaurus</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Carnotaurus sastrei</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="7">
         <f>IF(F45="","",F45-E45)</f>
         <v/>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>spinosaurus</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Spinosaurus aegyptiacus</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="7">
         <f>IF(F46="","",F46-E46)</f>
         <v/>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>Arrasa la ribera</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, 3 de daño al hábitat rival.</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr"/>
+      <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>mosasaurus</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Mosasaurus hoffmannii</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Reptil marino</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="7">
         <f>IF(F47="","",F47-E47)</f>
         <v/>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Devora el registro</t>
         </is>
       </c>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, el rival pierde 3 cartas de su mazo.</t>
         </is>
       </c>
-      <c r="L47" s="9" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>halszkaraptor</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Halszkaraptor escuilliei</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7">
         <f>IF(F48="","",F48-E48)</f>
         <v/>
       </c>
-      <c r="H48" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr"/>
+      <c r="L48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>tongtianlong</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Tongtianlong limosus</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="6">
+      <c r="E49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="7">
         <f>IF(F49="","",F49-E49)</f>
         <v/>
       </c>
-      <c r="H49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="7" t="n">
+      <c r="H49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>scanisaurus</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Scanisaurus nazarowi</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Reptil marino</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="E50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="7">
         <f>IF(F50="","",F50-E50)</f>
         <v/>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr"/>
+      <c r="L50" s="10" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>monolophosaurus</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Monolophosaurus jiangi</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="6">
+      <c r="E51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="7">
         <f>IF(F51="","",F51-E51)</f>
         <v/>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="H51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="I51" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>invictarx</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Invictarx zephyri</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="6">
+      <c r="E52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="7">
         <f>IF(F52="","",F52-E52)</f>
         <v/>
       </c>
-      <c r="H52" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" s="7" t="n">
+      <c r="H52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L52" s="9" t="inlineStr"/>
+      <c r="L52" s="10" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>medusaceratops</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Medusaceratops lokii</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="7">
         <f>IF(F53="","",F53-E53)</f>
         <v/>
       </c>
-      <c r="H53" s="7" t="n">
+      <c r="H53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="I53" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L53" s="9" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>platyceratops</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Platyceratops tatarinovi</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="6">
+      <c r="E54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7">
         <f>IF(F54="","",F54-E54)</f>
         <v/>
       </c>
-      <c r="H54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="7" t="n">
+      <c r="H54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L54" s="9" t="inlineStr"/>
+      <c r="L54" s="10" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>loricatosaurus</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Loricatosaurus priscus</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="7">
         <f>IF(F55="","",F55-E55)</f>
         <v/>
       </c>
-      <c r="H55" s="7" t="n">
+      <c r="H55" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="I55" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L55" s="9" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>therizinosaurus</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Therizinosaurus cheloniformis</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="7">
         <f>IF(F56="","",F56-E56)</f>
         <v/>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H56" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="I56" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr"/>
+      <c r="L56" s="10" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>alaskacephale</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Alaskacephale gangloffi</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="6">
+      <c r="E57" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="7">
         <f>IF(F57="","",F57-E57)</f>
         <v/>
       </c>
-      <c r="H57" s="7" t="n">
+      <c r="H57" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I57" s="7" t="n">
+      <c r="I57" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>titanoceratops</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Titanoceratops ouranos</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="7">
         <f>IF(F58="","",F58-E58)</f>
         <v/>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H58" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="I58" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J58" s="8" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr"/>
+      <c r="L58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>atlasaurus</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Atlasaurus imelakei</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="7">
         <f>IF(F59="","",F59-E59)</f>
         <v/>
       </c>
-      <c r="H59" s="7" t="n">
+      <c r="H59" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="I59" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J59" s="8" t="inlineStr">
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>Ramoneo alto</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, ganas 2 de Biomasa.</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>stegoceras</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Stegoceras validum</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="6">
+      <c r="E60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="7">
         <f>IF(F60="","",F60-E60)</f>
         <v/>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="H60" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="I60" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J60" s="8" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr"/>
+      <c r="L60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>maiasaura</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Maiasaura peeblesorum</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="7">
         <f>IF(F61="","",F61-E61)</f>
         <v/>
       </c>
-      <c r="H61" s="7" t="n">
+      <c r="H61" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I61" s="7" t="n">
+      <c r="I61" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L61" s="9" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>edmontosaurus</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Edmontosaurus annectens</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="7">
         <f>IF(F62="","",F62-E62)</f>
         <v/>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H62" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="I62" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="J62" s="8" t="inlineStr">
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr"/>
+      <c r="L62" s="10" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>plateosauravus</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Plateosauravus cullingworthi</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="6">
+      <c r="E63" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="7">
         <f>IF(F63="","",F63-E63)</f>
         <v/>
       </c>
-      <c r="H63" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" s="7" t="n">
+      <c r="H63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J63" s="8" t="inlineStr">
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K63" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>gargoyleosaurus</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Gargoyleosaurus parkpinorum</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Rara</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G64" s="6">
+      <c r="E64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="7">
         <f>IF(F64="","",F64-E64)</f>
         <v/>
       </c>
-      <c r="H64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I64" s="7" t="n">
+      <c r="H64" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J64" s="8" t="inlineStr">
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>Cierra la formación</t>
         </is>
       </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K64" s="10" t="inlineStr">
         <is>
           <t>Al entrar en juego, tus otros dinosaurios curan 2 heridas.</t>
         </is>
       </c>
-      <c r="L64" s="9" t="inlineStr"/>
+      <c r="L64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>wendiceratops</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Wendiceratops pinhornensis</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="7">
         <f>IF(F65="","",F65-E65)</f>
         <v/>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="H65" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="I65" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J65" s="8" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L65" s="9" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>antarctosaurus</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Antarctosaurus wichmannianus</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>Legendaria</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="7">
         <f>IF(F66="","",F66-E66)</f>
         <v/>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="I66" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="J66" s="8" t="inlineStr">
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L66" s="9" t="inlineStr"/>
+      <c r="L66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>liaoceratops</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Liaoceratops yanzigouensis</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="6">
+      <c r="E67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="7">
         <f>IF(F67="","",F67-E67)</f>
         <v/>
       </c>
-      <c r="H67" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="7" t="n">
+      <c r="H67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J67" s="8" t="inlineStr">
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>rhinorex</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Rhinorex condrupus</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="7">
         <f>IF(F68="","",F68-E68)</f>
         <v/>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="I68" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J68" s="8" t="inlineStr">
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K68" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>bienosaurus</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Bienosaurus lufengensis</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="6">
+      <c r="E69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
         <f>IF(F69="","",F69-E69)</f>
         <v/>
       </c>
-      <c r="H69" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" s="7" t="n">
+      <c r="H69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J69" s="8" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>shuangmiaosaurus</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Shuangmiaosaurus gilmorei</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" s="6">
+      <c r="E70" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="7">
         <f>IF(F70="","",F70-E70)</f>
         <v/>
       </c>
-      <c r="H70" s="7" t="n">
+      <c r="H70" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I70" s="7" t="n">
+      <c r="I70" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J70" s="8" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr"/>
+      <c r="L70" s="10" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>chasmosaurus</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Chasmosaurus belli</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Común</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="6">
+      <c r="E71" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7">
         <f>IF(F71="","",F71-E71)</f>
         <v/>
       </c>
-      <c r="H71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" s="7" t="n">
+      <c r="H71" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J71" s="8" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>Sin rasgo</t>
         </is>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="10" t="inlineStr">
         <is>
           <t>Todavía no hace nada especial.</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:K71"/>
@@ -3814,7 +4082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3884,1138 +4152,1138 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Depredador dominante</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Allosaurus fragilis, Saurophaganax maximus</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Gregario</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Dryosaurus altus, Brachylophosaurus canadensis</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Ataque por cada congénere en el campo</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>rasgos.gregarioAtaquePorCompanero</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Manada</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Apatosaurus louisae, Barosaurus lentus</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Vida con otro del mismo clado</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>rasgos.manadaVida</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Troodon formosus</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, robas 1 carta.</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>cartas que robas al entrar</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>entradas.alertaRoba</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Arrasa la ribera</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Spinosaurus aegyptiacus</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, 3 de daño al hábitat rival.</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>de daño al hábitat rival, al entrar</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>entradas.arrasaHabitat</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>heridas que curan los saurópodos</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>efectosCampo.bosqueCura</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Canal fluvial trenzado</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Vida a todos los del campo</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>efectosCampo.canalVida</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Carroña abundante</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Caza en grupo</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Ceratosaurus nasicornis</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="E13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Ataque si hay bastantes copias en el campo</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>rasgos.cazaEnGrupoAtaque</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Cierra la formación</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Gargoyleosaurus parkpinorum</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, tus otros dinosaurios curan 2 heridas.</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>heridas que curan tus OTROS dinosaurios</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>entradas.manadaSanaCura</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Competencia trófica</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="E15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Vida que se quita, a dos rivales</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>rasgos.competenciaVida</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Crecimiento acelerado</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="E16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Ataque, y otro tanto de Vida</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>rasgos.crecimientoAtaque</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Deriva árida</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Ambos jugadores pierden 5 cartas del mazo</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>cartas de mazo que pierden los DOS</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>efectosCampo.aridezMazo</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Desgarro</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Tyrannotitan chubutensis</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>A quien hiere no se le cura ninguna herida ese turno.</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Devora el registro</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Mosasaurus hoffmannii</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, el rival pierde 3 cartas de su mazo.</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>cartas de mazo que pierde el rival</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>entradas.devoraMazo</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="B20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Dromaeosaurus albertensis</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, hace 3 de daño al dinosaurio que tenga enfrente.</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>de daño al que tenga enfrente, al entrar</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>entradas.emboscadaDano</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="B21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Fractura consolidada</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="E21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Ataque que se quita</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>rasgos.fracturaAtaque</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="B22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Gastrolitos</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Cura +1 de vida a un dinosaurio al final del turno</t>
         </is>
       </c>
-      <c r="E22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="E22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>heridas curadas a un dinosaurio</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>rasgos.gastrolitosCura</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Gola ornamentada</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Lokiceratops rangiformis</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="E23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Vida con otra copia en el campo</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>rasgos.golaVida</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Gregarismo</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="E24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Ataque a toda la especie</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>rasgos.gregarismoAtaque</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Lago efímero</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Llamada de manada</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="B26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Nodosaurus textilis</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Llanura de inundación</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="E27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>cambio de carta por turno y jugador</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>efectosCampo.llanuraReciclaPorTurno</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Migrador</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Camarasaurus grandis</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Mortandad estacional</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>de daño a TODOS, incluidos los tuyos</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>rasgos.mortandadDano</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Muro de placas</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="B30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Stegosaurus stenops</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="E30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Vida con otra copia en el campo</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>rasgos.muroDePlacasVida</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="B31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Neumaticidad ósea</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="E31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Ataque permanente</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>rasgos.neumaticidadAtaque</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Oportunista</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="B32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Ornitholestes hermanni</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
         </is>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="E32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Vida permanente por cada muerte</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>rasgos.oportunistaVidaPorMuerte</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Ramoneo alto</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="B33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Atlasaurus imelakei</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Al entrar en juego, ganas 2 de Biomasa.</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="E33" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Biomasa que ganas al entrar</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>entradas.ramoneoBiomasa</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Ramoneo bajo</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Diplodocus carnegii</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
         </is>
       </c>
-      <c r="E34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="E34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>heridas curadas al final del turno</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>rasgos.ramoneoBajoCura</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Rastreador</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="B35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Torvosaurus tanneri</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="B36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Rebrote tras incendio</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Ribereño</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="B37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Riparovenator milnerae</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="E37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Ataque con el Canal en el campo</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>rasgos.riberenoAtaque</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="B38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Sabana de helechos</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="E38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Biomasa por turno a los DOS</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>efectosCampo.sabanaBiomasa</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="B39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Trampa de depredadores</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>cartas que pierde el rival</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>rasgos.trampaMazoRival</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Huaxiadraco corollatus</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr"/>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>no lleva número: es una regla, no una cifra</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5025,7 +5293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5077,380 +5345,380 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Tablero</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Ranuras enfrentadas</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Cada una pelea contra la de enfrente</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Tablero</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Vida del hábitat</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Llegar a 0 pierde la partida</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Tablero</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trofeos para ganar</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Cada baja rival es un trofeo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Tablero</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Límite de turnos</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Se decide por trofeos y luego por hábitat</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Mano</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Mano inicial</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Se puede cambiar entera una vez (mulligan)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Mano</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Mano máxima</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Por encima hay que descartar</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Mazo</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Cartas del mazo</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Quedarse sin mazo pierde la partida</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Economía</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Renta por turno</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="C12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Biomasa, plana, igual para los dos</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Combate</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Daño de un golpe</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>el Ataque</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Sin restas: no hay Defensa ni suelo de daño</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Combate</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Bonus de depredación</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Terópodo contra ornitópodo</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Combate</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Púas del tireóforo</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="C15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Se devuelven a quien le ataque</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Combate</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Daño sobrante</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>sí pasa</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Lo que sobra al matar sigue al hábitat rival</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Colección</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Precio del sobre</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>5 cartas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Colección</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Monedas por victoria</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Perder no paga nada</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Colección</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Monedas de inicio</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Rareza</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Copias por mazo · comun</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Fundir una copia sobrante da 4 monedas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Rareza</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Copias por mazo · raro</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Fundir una copia sobrante da 12 monedas</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Rareza</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Copias por mazo · epico</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="C22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Fundir una copia sobrante da 35 monedas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Rareza</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Copias por mazo · legendario</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Fundir una copia sobrante da 100 monedas</t>
         </is>
@@ -5464,7 +5732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5522,147 +5790,147 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Ornitópodo</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>es la presa del terópodo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Terópodo</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="4" t="n">
         <v>5.2</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="4" t="n">
         <v>4.9</v>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>+2 de daño contra ornitópodos</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Tireóforo</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>7.5</v>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>devuelve 2 de daño a quien le ataque</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Saurópodo</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="4" t="n">
         <v>11.3</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>sin regla propia</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Marginocéfalo</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="4" t="n">
         <v>3.3</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>sin regla propia</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Pterosaurio</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="10" t="n">
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>sin regla propia</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Reptil marino</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>sin regla propia</t>
         </is>
@@ -5676,7 +5944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5716,272 +5984,272 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>dryosaurus</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ornitholestes</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ceratosaurus</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>nodosaurus</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>stegosaurus</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>allosaurus</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>camarasaurus</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>riparovenator</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>lokiceratops</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>brachylophosaurus</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>huaxiadraco</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>diplodocus</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>apatosaurus</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>torvosaurus</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>tyrannotitan</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>gregarismo</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>trampa</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>rebrote</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>gastrolitos</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>fractura</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>sabana</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>aridez</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>mortandad</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>crecimiento_acelerado</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>neumaticidad</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>competencia</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5993,7 +6261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>11.03 turnos</t>
+          <t>11.65 turnos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>49.8 %</t>
+          <t>49.0 %</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>36% / 44% / 19%</t>
+          <t>51% / 35% / 14%</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>FALLA</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>índice 0.00, uso 0 % (coste 3)</t>
+          <t>índice 0.00, uso 0 % (coste 1)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -736,12 +736,12 @@
       <c r="A14" s="4" t="inlineStr"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>índice 0.32, uso 26 % (coste 1)</t>
+          <t>índice 0.00, uso 0 % (coste 3)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
@@ -750,29 +750,15 @@
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Torvosaurus tanneri</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>índice 0.70, uso 68 % (coste 4)</t>
+          <t>índice 0.50, uso 45 % (coste 1)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Gregarismo</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>índice 1.69, uso 95 % (coste 1)</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -925,16 +911,8 @@
       <c r="I6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Gregario</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
-        </is>
-      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
       <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -974,16 +952,8 @@
       <c r="I7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Oportunista</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
-        </is>
-      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr"/>
       <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -1023,16 +993,8 @@
       <c r="I8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Caza en grupo</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
-        </is>
-      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr"/>
       <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1072,16 +1034,8 @@
       <c r="I9" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Muro de placas</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
-        </is>
-      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
       <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -1121,16 +1075,8 @@
       <c r="I10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Depredador dominante</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
-        </is>
-      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
       <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1170,16 +1116,8 @@
       <c r="I11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Migrador</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr"/>
       <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1219,16 +1157,8 @@
       <c r="I12" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>Ramoneo bajo</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
-        </is>
-      </c>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr"/>
       <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -1268,16 +1198,8 @@
       <c r="I13" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Manada</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
-        </is>
-      </c>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
       <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -1317,16 +1239,8 @@
       <c r="I14" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>Rastreador</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr"/>
       <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -1366,16 +1280,8 @@
       <c r="I15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Llamada de manada</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
       <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1415,16 +1321,8 @@
       <c r="I16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Ribereño</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
-        </is>
-      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr"/>
       <c r="L16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1464,16 +1362,8 @@
       <c r="I17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Gola ornamentada</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
-        </is>
-      </c>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr"/>
       <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1513,16 +1403,8 @@
       <c r="I18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Gregario</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>+1 Poder por cada copia suya que tengas en el campo.</t>
-        </is>
-      </c>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr"/>
       <c r="L18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -1562,16 +1444,8 @@
       <c r="I19" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>Desgarro</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>A quien hiere no se le cura ninguna herida ese turno.</t>
-        </is>
-      </c>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr"/>
       <c r="L19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1611,16 +1485,8 @@
       <c r="I20" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Vuelo</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
-        </is>
-      </c>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
       <c r="L20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -2380,16 +2246,8 @@
       <c r="I37" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J37" s="9" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -2429,16 +2287,8 @@
       <c r="I38" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J38" s="9" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -2478,16 +2328,8 @@
       <c r="I39" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Emboscada</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, hace 3 de daño al dinosaurio que tenga enfrente.</t>
-        </is>
-      </c>
+      <c r="J39" s="9" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2527,16 +2369,8 @@
       <c r="I40" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J40" s="9" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -2576,16 +2410,8 @@
       <c r="I41" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J41" s="9" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
       <c r="L41" s="10" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
@@ -2625,16 +2451,8 @@
       <c r="I42" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J42" s="9" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
@@ -2674,16 +2492,8 @@
       <c r="I43" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J43" s="9" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
@@ -2723,16 +2533,8 @@
       <c r="I44" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Alerta</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, robas 1 carta.</t>
-        </is>
-      </c>
+      <c r="J44" s="9" t="inlineStr"/>
+      <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
@@ -2772,16 +2574,8 @@
       <c r="I45" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J45" s="9" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
@@ -2821,16 +2615,8 @@
       <c r="I46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>Arrasa la ribera</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, 3 de daño al hábitat rival.</t>
-        </is>
-      </c>
+      <c r="J46" s="9" t="inlineStr"/>
+      <c r="K46" s="10" t="inlineStr"/>
       <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
@@ -2870,16 +2656,8 @@
       <c r="I47" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Devora el registro</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, el rival pierde 3 cartas de su mazo.</t>
-        </is>
-      </c>
+      <c r="J47" s="9" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
@@ -2919,16 +2697,8 @@
       <c r="I48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J48" s="9" t="inlineStr"/>
+      <c r="K48" s="10" t="inlineStr"/>
       <c r="L48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
@@ -2968,16 +2738,8 @@
       <c r="I49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J49" s="9" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr"/>
       <c r="L49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -3017,16 +2779,8 @@
       <c r="I50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J50" s="9" t="inlineStr"/>
+      <c r="K50" s="10" t="inlineStr"/>
       <c r="L50" s="10" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
@@ -3066,16 +2820,8 @@
       <c r="I51" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K51" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J51" s="9" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
@@ -3115,16 +2861,8 @@
       <c r="I52" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K52" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J52" s="9" t="inlineStr"/>
+      <c r="K52" s="10" t="inlineStr"/>
       <c r="L52" s="10" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
@@ -3164,16 +2902,8 @@
       <c r="I53" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J53" s="9" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
@@ -3213,16 +2943,8 @@
       <c r="I54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J54" s="9" t="inlineStr"/>
+      <c r="K54" s="10" t="inlineStr"/>
       <c r="L54" s="10" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
@@ -3262,16 +2984,8 @@
       <c r="I55" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J55" s="9" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
@@ -3311,16 +3025,8 @@
       <c r="I56" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K56" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="10" t="inlineStr"/>
       <c r="L56" s="10" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
@@ -3360,16 +3066,8 @@
       <c r="I57" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J57" s="9" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
       <c r="L57" s="10" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
@@ -3409,16 +3107,8 @@
       <c r="I58" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J58" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K58" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J58" s="9" t="inlineStr"/>
+      <c r="K58" s="10" t="inlineStr"/>
       <c r="L58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
@@ -3458,16 +3148,8 @@
       <c r="I59" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Ramoneo alto</t>
-        </is>
-      </c>
-      <c r="K59" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, ganas 2 de Biomasa.</t>
-        </is>
-      </c>
+      <c r="J59" s="9" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
       <c r="L59" s="10" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
@@ -3507,16 +3189,8 @@
       <c r="I60" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J60" s="9" t="inlineStr"/>
+      <c r="K60" s="10" t="inlineStr"/>
       <c r="L60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
@@ -3556,16 +3230,8 @@
       <c r="I61" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J61" s="9" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
       <c r="L61" s="10" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
@@ -3605,16 +3271,8 @@
       <c r="I62" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="10" t="inlineStr"/>
       <c r="L62" s="10" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
@@ -3654,16 +3312,8 @@
       <c r="I63" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K63" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
       <c r="L63" s="10" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
@@ -3703,16 +3353,8 @@
       <c r="I64" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>Cierra la formación</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, tus otros dinosaurios curan 2 heridas.</t>
-        </is>
-      </c>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="10" t="inlineStr"/>
       <c r="L64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -3752,16 +3394,8 @@
       <c r="I65" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K65" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
       <c r="L65" s="10" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
@@ -3801,16 +3435,8 @@
       <c r="I66" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K66" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="10" t="inlineStr"/>
       <c r="L66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
@@ -3850,16 +3476,8 @@
       <c r="I67" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K67" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J67" s="9" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
       <c r="L67" s="10" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
@@ -3899,16 +3517,8 @@
       <c r="I68" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J68" s="9" t="inlineStr"/>
+      <c r="K68" s="10" t="inlineStr"/>
       <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -3948,16 +3558,8 @@
       <c r="I69" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J69" s="9" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
       <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
@@ -3997,16 +3599,8 @@
       <c r="I70" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K70" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J70" s="9" t="inlineStr"/>
+      <c r="K70" s="10" t="inlineStr"/>
       <c r="L70" s="10" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -4046,16 +3640,8 @@
       <c r="I71" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>Sin rasgo</t>
-        </is>
-      </c>
-      <c r="K71" s="10" t="inlineStr">
-        <is>
-          <t>Todavía no hace nada especial.</t>
-        </is>
-      </c>
+      <c r="J71" s="9" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
       <c r="L71" s="10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4088,7 +3674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4154,47 +3740,53 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Depredador dominante</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Allosaurus fragilis, Saurophaganax maximus</t>
+          <t>Bosque de coníferas ribereño</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Si mata a su rival, el daño sobrante que pasa al hábitat enemigo se duplica.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+          <t>heridas que curan los saurópodos</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>efectosCampo.bosqueCura</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Gregario</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Dryosaurus altus, Brachylophosaurus canadensis</t>
+          <t>Canal fluvial trenzado</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>+1 de Ataque por cada otro Dryosaurus propio en el campo.</t>
+          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -4202,52 +3794,46 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Ataque por cada congénere en el campo</t>
+          <t>Vida a todos los del campo</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>rasgos.gregarioAtaquePorCompanero</t>
+          <t>efectosCampo.canalVida</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Manada</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Apatosaurus louisae, Barosaurus lentus</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+1 de Vida si tienes otro saurópodo en el campo.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Vida con otro del mismo clado</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.manadaVida</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Alerta</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -4255,32 +3841,32 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Troodon formosus</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Al entrar en juego, robas 1 carta.</t>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cartas que robas al entrar</t>
+          <t>Vida que se quita, a dos rivales</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>entradas.alertaRoba</t>
+          <t>rasgos.competenciaVida</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Arrasa la ribera</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -4288,32 +3874,32 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Spinosaurus aegyptiacus</t>
+          <t>Crecimiento acelerado</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Al entrar en juego, 3 de daño al hábitat rival.</t>
+          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>de daño al hábitat rival, al entrar</t>
+          <t>Ataque, y otro tanto de Vida</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>entradas.arrasaHabitat</t>
+          <t>rasgos.crecimientoAtaque</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -4321,32 +3907,32 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Deriva árida</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+          <t>Ambos jugadores pierden 5 cartas del mazo</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>heridas que curan los saurópodos</t>
+          <t>cartas de mazo que pierden los DOS</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.bosqueCura</t>
+          <t>efectosCampo.aridezMazo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -4354,32 +3940,32 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Fractura consolidada</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
+          <t>−2 Poder permanente a un dinosaurio rival.</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Vida a todos los del campo</t>
+          <t>Ataque que se quita</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.canalVida</t>
+          <t>rasgos.fracturaAtaque</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -4387,26 +3973,32 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Gastrolitos</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
+          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
+          <t>heridas curadas a un dinosaurio</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.gastrolitosCura</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Caza en grupo</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -4414,32 +4006,32 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ceratosaurus nasicornis</t>
+          <t>Gregarismo</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>+2 de Ataque si hay tres Ceratosaurus tuyos en el campo.</t>
+          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Ataque si hay bastantes copias en el campo</t>
+          <t>Ataque a toda la especie</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>rasgos.cazaEnGrupoAtaque</t>
+          <t>rasgos.gregarismoAtaque</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Cierra la formación</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -4447,32 +4039,26 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Gargoyleosaurus parkpinorum</t>
+          <t>Lago efímero</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Al entrar en juego, tus otros dinosaurios curan 2 heridas.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>heridas que curan tus OTROS dinosaurios</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>entradas.manadaSanaCura</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -4480,32 +4066,32 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Llanura de inundación</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Vida que se quita, a dos rivales</t>
+          <t>cambio de carta por turno y jugador</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>rasgos.competenciaVida</t>
+          <t>efectosCampo.llanuraReciclaPorTurno</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Mortandad estacional</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -4513,32 +4099,32 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Crecimiento acelerado</t>
+          <t>Mortandad estacional</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+2 Poder y +2 Vida permanentes a un dinosaurio que elijas.</t>
+          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Ataque, y otro tanto de Vida</t>
+          <t>de daño a TODOS, incluidos los tuyos</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>rasgos.crecimientoAtaque</t>
+          <t>rasgos.mortandadDano</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Neumaticidad ósea</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -4546,32 +4132,32 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Neumaticidad ósea</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Ambos jugadores pierden 5 cartas del mazo</t>
+          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>cartas de mazo que pierden los DOS</t>
+          <t>Ataque permanente</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.aridezMazo</t>
+          <t>rasgos.neumaticidadAtaque</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Desgarro</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -4579,12 +4165,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Tyrannotitan chubutensis</t>
+          <t>Rebrote tras incendio</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>A quien hiere no se le cura ninguna herida ese turno.</t>
+          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -4598,7 +4184,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Devora el registro</t>
+          <t>Sabana de helechos</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -4606,32 +4192,32 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Mosasaurus hoffmannii</t>
+          <t>Sabana de helechos</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Al entrar en juego, el rival pierde 3 cartas de su mazo.</t>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>cartas de mazo que pierde el rival</t>
+          <t>Biomasa por turno a los DOS</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>entradas.devoraMazo</t>
+          <t>efectosCampo.sabanaBiomasa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Emboscada</t>
+          <t>Trampa de depredadores</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
@@ -4639,651 +4225,27 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Dromaeosaurus albertensis</t>
+          <t>Trampa de depredadores</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Al entrar en juego, hace 3 de daño al dinosaurio que tenga enfrente.</t>
+          <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>de daño al que tenga enfrente, al entrar</t>
+          <t>cartas que pierde el rival</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>entradas.emboscadaDano</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Fractura consolidada</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Fractura consolidada</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>−2 Poder permanente a un dinosaurio rival.</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Ataque que se quita</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.fracturaAtaque</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Gastrolitos</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Gastrolitos</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Cura +1 de vida a un dinosaurio al final del turno</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>heridas curadas a un dinosaurio</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.gastrolitosCura</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Gola ornamentada</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Lokiceratops rangiformis</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>+2 de Vida si tienes otro Lokiceratops en el campo.</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Vida con otra copia en el campo</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.golaVida</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Gregarismo</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Gregarismo</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>+1 de Ataque a todos tus dinosaurios de la misma especie que el objetivo.</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Ataque a toda la especie</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.gregarismoAtaque</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Lago efímero</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Lago efímero</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>+2 Biomasa ahora mismo. Tu hábitat pierde 2 puntos.</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Llamada de manada</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Nodosaurus textilis</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un Gregarismo en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Llanura de inundación</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Llanura de inundación</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>cambio de carta por turno y jugador</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.llanuraReciclaPorTurno</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Migrador</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Camarasaurus grandis</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un evento en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Mortandad estacional</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Mortandad estacional</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>3 de daño a TODOS los dinosaurios del campo, incluidos los tuyos.</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>de daño a TODOS, incluidos los tuyos</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.mortandadDano</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Muro de placas</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Stegosaurus stenops</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>+1 de Vida si tienes otro Stegosaurus en el campo.</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Vida con otra copia en el campo</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.muroDePlacasVida</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Neumaticidad ósea</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Neumaticidad ósea</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>+2 de Ataque permanentes. Sólo sobre terópodos y saurópodos.</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Ataque permanente</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.neumaticidadAtaque</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Oportunista</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Ornitholestes hermanni</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>+1 Vida permanente cada vez que muere un dinosaurio en el campo.</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Vida permanente por cada muerte</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.oportunistaVidaPorMuerte</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Ramoneo alto</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Atlasaurus imelakei</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Al entrar en juego, ganas 2 de Biomasa.</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Biomasa que ganas al entrar</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>entradas.ramoneoBiomasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ramoneo bajo</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Diplodocus carnegii</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Recupera +1 de vida al final de cada uno de tus turnos</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>heridas curadas al final del turno</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.ramoneoBajoCura</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Rastreador</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Torvosaurus tanneri</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Al jugarla, busca un clima en tu mazo y llévatelo a la mano.</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Rebrote tras incendio</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Rebrote tras incendio</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>+2 Biomasa ahora mismo. Todos tus dinosaurios reciben 1 herida.</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Ribereño</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Riparovenator milnerae</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>+2 de ataque mientras el Canal fluvial esté en el campo.</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Ataque con el Canal en el campo</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>rasgos.riberenoAtaque</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Sabana de helechos</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Sabana de helechos</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Biomasa por turno a los DOS</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.sabanaBiomasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Trampa de depredadores</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Trampa de depredadores</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>El rival pierde 5 cartas de su mazo. Tú pierdes 3: el fango no distingue.</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>cartas que pierde el rival</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
           <t>rasgos.trampaMazoRival</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Vuelo</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Huaxiadraco corollatus</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Sobrevuela la ranura: golpea siempre al hábitat rival, pero quien tenga enfrente le alcanza igual.</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5299,7 +4261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5534,15 +4496,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Bonus de depredación</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2</v>
+          <t>Reglas de clado</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ninguna</t>
+        </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Terópodo contra ornitópodo</t>
+          <t>El clado es clasificación, no cambia números</t>
         </is>
       </c>
     </row>
@@ -5554,37 +4518,37 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Púas del tireóforo</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2</v>
+          <t>Daño sobrante</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>sí pasa</t>
+        </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Se devuelven a quien le ataque</t>
+          <t>Lo que sobra al matar sigue al hábitat rival</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Combate</t>
+          <t>Colección</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Daño sobrante</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>sí pasa</t>
-        </is>
+          <t>Precio del sobre</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Lo que sobra al matar sigue al hábitat rival</t>
+          <t>5 cartas</t>
         </is>
       </c>
     </row>
@@ -5596,15 +4560,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Precio del sobre</t>
+          <t>Monedas por victoria</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>5 cartas</t>
+          <t>Perder no paga nada</t>
         </is>
       </c>
     </row>
@@ -5616,33 +4580,33 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Monedas por victoria</t>
+          <t>Monedas de inicio</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Perder no paga nada</t>
-        </is>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Colección</t>
+          <t>Rareza</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Monedas de inicio</t>
+          <t>Copias por mazo · comun</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>240</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Fundir una copia sobrante da 4 monedas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5652,7 +4616,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Copias por mazo · comun</t>
+          <t>Copias por mazo · raro</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -5660,7 +4624,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Fundir una copia sobrante da 4 monedas</t>
+          <t>Fundir una copia sobrante da 12 monedas</t>
         </is>
       </c>
     </row>
@@ -5672,15 +4636,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Copias por mazo · raro</t>
+          <t>Copias por mazo · epico</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Fundir una copia sobrante da 12 monedas</t>
+          <t>Fundir una copia sobrante da 35 monedas</t>
         </is>
       </c>
     </row>
@@ -5692,33 +4656,13 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Copias por mazo · epico</t>
+          <t>Copias por mazo · legendario</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Fundir una copia sobrante da 35 monedas</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Rareza</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Copias por mazo · legendario</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Fundir una copia sobrante da 100 monedas</t>
         </is>
@@ -5806,7 +4750,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>es la presa del terópodo</t>
+          <t>sin regla propia</t>
         </is>
       </c>
     </row>
@@ -5827,7 +4771,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+2 de daño contra ornitópodos</t>
+          <t>sin regla propia</t>
         </is>
       </c>
     </row>
@@ -5848,7 +4792,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>devuelve 2 de daño a quien le ataque</t>
+          <t>sin regla propia</t>
         </is>
       </c>
     </row>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estado" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mecánicas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clados" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mazo de referencia" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clados" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mazo de referencia" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartas'!$A$5:$K$71</definedName>
@@ -574,7 +575,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>11.65 turnos</t>
+          <t>11.43 turnos</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -596,7 +597,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>49.0 %</t>
+          <t>46.1 %</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -606,7 +607,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>cumple</t>
+          <t>FALLA</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>68.2 %</t>
+          <t>66.6 %</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -684,7 +685,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>51% / 35% / 14%</t>
+          <t>36% / 44% / 20%</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -694,7 +695,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>FALLA</t>
+          <t>cumple</t>
         </is>
       </c>
     </row>
@@ -755,7 +756,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>índice 0.50, uso 45 % (coste 1)</t>
+          <t>índice 0.61, uso 53 % (coste 1)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -911,8 +912,16 @@
       <c r="I6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Bandada nerviosa</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Dryosaurus en juego, sea de quien sea y este incluido.</t>
+        </is>
+      </c>
       <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -952,8 +961,16 @@
       <c r="I7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Salto de entrada</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+        </is>
+      </c>
       <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -978,23 +995,31 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",F8-E8)</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Ayuno del cazador</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 2 cartas de tu mazo.</t>
+        </is>
+      </c>
       <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1032,10 +1057,18 @@
         <v>1</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Muro de placas</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Stegosaurus que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -1075,8 +1108,16 @@
       <c r="I10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Zarpazo por sorpresa</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 1 carta al azar de la mano de tu rival.</t>
+        </is>
+      </c>
       <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1111,13 +1152,21 @@
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="9" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Rumia</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Al final de tu turno recupera 1 de Vida.</t>
+        </is>
+      </c>
       <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1138,7 +1187,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1155,10 +1204,18 @@
         <v>3</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Pisa y abona</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
+        </is>
+      </c>
       <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -1179,7 +1236,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -1196,10 +1253,18 @@
         <v>2</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="9" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Pisa y abona</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
+        </is>
+      </c>
       <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -1220,7 +1285,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Legendaria</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1234,13 +1299,21 @@
         <v/>
       </c>
       <c r="H14" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Indiferente al cielo</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>No le afectan los efectos del clima.</t>
+        </is>
+      </c>
       <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -1261,27 +1334,35 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Rara</t>
+          <t>Épica</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",F15-E15)</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Indiferente al cielo</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>No le afectan los efectos del clima.</t>
+        </is>
+      </c>
       <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -1306,23 +1387,31 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",F16-E16)</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="9" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Fuera del alcance</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>No le afectan las cartas de evento de tu rival.</t>
+        </is>
+      </c>
       <c r="L16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1360,10 +1449,18 @@
         <v>4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" s="9" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Fuera del alcance</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>No le afectan las cartas de evento de tu rival.</t>
+        </is>
+      </c>
       <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1398,13 +1495,21 @@
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Rebaño de tres</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Si llegas a tener 3 Brachylophosaurus en juego, éste gana +6 de Ataque para siempre.</t>
+        </is>
+      </c>
       <c r="L18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -1442,10 +1547,18 @@
         <v>10</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="9" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Tijera</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 4 de Vida.</t>
+        </is>
+      </c>
       <c r="L19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -1485,8 +1598,16 @@
       <c r="I20" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="9" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Vuelo de reconocimiento</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego robas 1 carta.</t>
+        </is>
+      </c>
       <c r="L20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -2241,13 +2362,21 @@
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="9" t="inlineStr"/>
-      <c r="K37" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Sigue a los grandes</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
+        </is>
+      </c>
       <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -2282,13 +2411,21 @@
         <v/>
       </c>
       <c r="H38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I38" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="9" t="inlineStr"/>
-      <c r="K38" s="10" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Salto de entrada</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+        </is>
+      </c>
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -2323,13 +2460,21 @@
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="9" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Jauría</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Dromaeosaurus en juego, sea de quien sea y este incluido.</t>
+        </is>
+      </c>
       <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2367,10 +2512,18 @@
         <v>2</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="9" t="inlineStr"/>
-      <c r="K40" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Olfato de tormenta</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarlo, puedes llevarte a la mano una carta de evento de tu mazo.</t>
+        </is>
+      </c>
       <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -2405,13 +2558,21 @@
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="9" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Olfato de tormenta</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarlo, puedes llevarte a la mano una carta de clima de tu mazo.</t>
+        </is>
+      </c>
       <c r="L41" s="10" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
@@ -2446,13 +2607,21 @@
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="9" t="inlineStr"/>
-      <c r="K42" s="10" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Rastreo de orilla</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
+        </is>
+      </c>
       <c r="L42" s="10" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
@@ -2477,23 +2646,31 @@
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",F43-E43)</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="9" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Percha compartida</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Vida por cada Eosinopteryx que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L43" s="10" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
@@ -2518,23 +2695,31 @@
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="7">
         <f>IF(F44="","",F44-E44)</f>
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="9" t="inlineStr"/>
-      <c r="K44" s="10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Caza coordinada</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Troodon que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L44" s="10" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
@@ -2569,13 +2754,21 @@
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="9" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Territorio exclusivo</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Para jugarlo tienes que descartar 2 cartas de tu mano.</t>
+        </is>
+      </c>
       <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1">
@@ -2610,13 +2803,21 @@
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J46" s="9" t="inlineStr"/>
-      <c r="K46" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>Draga el río</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+        </is>
+      </c>
       <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
@@ -2651,13 +2852,21 @@
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J47" s="9" t="inlineStr"/>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Draga el río</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+        </is>
+      </c>
       <c r="L47" s="10" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customHeight="1">
@@ -2678,7 +2887,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Común</t>
+          <t>Rara</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2697,8 +2906,16 @@
       <c r="I48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
-      <c r="K48" s="10" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Nadador de temporal</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
+        </is>
+      </c>
       <c r="L48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
@@ -2736,10 +2953,18 @@
         <v>1</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="9" t="inlineStr"/>
-      <c r="K49" s="10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>Nadador de temporal</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque mientras haya un clima en el campo.</t>
+        </is>
+      </c>
       <c r="L49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -2764,23 +2989,31 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" s="7">
         <f>IF(F50="","",F50-E50)</f>
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="9" t="inlineStr"/>
-      <c r="K50" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Banco de caza</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus reptiles marinos ganan +1 de Ataque.</t>
+        </is>
+      </c>
       <c r="L50" s="10" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
@@ -2805,23 +3038,31 @@
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51" s="7">
         <f>IF(F51="","",F51-E51)</f>
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="9" t="inlineStr"/>
-      <c r="K51" s="10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Cresta de mando</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus terópodos ganan +1 de Vida.</t>
+        </is>
+      </c>
       <c r="L51" s="10" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
@@ -2846,23 +3087,31 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",F52-E52)</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="9" t="inlineStr"/>
-      <c r="K52" s="10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>Formación cerrada</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus tireóforos ganan +1 de Vida.</t>
+        </is>
+      </c>
       <c r="L52" s="10" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
@@ -2897,13 +3146,21 @@
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J53" s="9" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Muralla de golas</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus marginocéfalos ganan +1 de Ataque y +1 de Vida.</t>
+        </is>
+      </c>
       <c r="L53" s="10" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
@@ -2941,10 +3198,18 @@
         <v>1</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="9" t="inlineStr"/>
-      <c r="K54" s="10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>Llamada de manada</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarlo, puedes llevarte a la mano otro Platyceratops de tu mazo.</t>
+        </is>
+      </c>
       <c r="L54" s="10" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
@@ -2965,7 +3230,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
@@ -2979,13 +3244,21 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J55" s="9" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Terraplén</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu hábitat recupera 2 puntos.</t>
+        </is>
+      </c>
       <c r="L55" s="10" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customHeight="1">
@@ -3006,7 +3279,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Común</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3020,13 +3293,21 @@
         <v/>
       </c>
       <c r="H56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J56" s="9" t="inlineStr"/>
-      <c r="K56" s="10" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>Garra de sequía</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Gana +3 de Ataque mientras haya un clima en el campo.</t>
+        </is>
+      </c>
       <c r="L56" s="10" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
@@ -3061,13 +3342,21 @@
         <v/>
       </c>
       <c r="H57" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="9" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>Testarazo</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+        </is>
+      </c>
       <c r="L57" s="10" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
@@ -3102,13 +3391,21 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="9" t="inlineStr"/>
-      <c r="K58" s="10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>Cuerno mayor</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada marginocéfalo que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
@@ -3143,13 +3440,21 @@
         <v/>
       </c>
       <c r="H59" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Sombra del cuello</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus saurópodos ganan +1 de Vida.</t>
+        </is>
+      </c>
       <c r="L59" s="10" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1">
@@ -3184,13 +3489,21 @@
         <v/>
       </c>
       <c r="H60" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J60" s="9" t="inlineStr"/>
-      <c r="K60" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>Cabezazo de vuelta</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
+        </is>
+      </c>
       <c r="L60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
@@ -3211,7 +3524,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Épica</t>
+          <t>Legendaria</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
@@ -3225,13 +3538,21 @@
         <v/>
       </c>
       <c r="H61" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>Buena madre</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
+        </is>
+      </c>
       <c r="L61" s="10" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
@@ -3266,13 +3587,21 @@
         <v/>
       </c>
       <c r="H62" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="J62" s="9" t="inlineStr"/>
-      <c r="K62" s="10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>Migración en masa</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus ornitópodos ganan +1 de Ataque y +1 de Vida.</t>
+        </is>
+      </c>
       <c r="L62" s="10" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
@@ -3310,10 +3639,18 @@
         <v>2</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="9" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>Colonia de ribera</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque y +1 de Vida por cada Plateosauravus que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L63" s="10" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
@@ -3351,10 +3688,18 @@
         <v>2</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="9" t="inlineStr"/>
-      <c r="K64" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>Osteodermos</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>Devuelve 3 de daño a quien lo hiera en combate.</t>
+        </is>
+      </c>
       <c r="L64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -3392,10 +3737,18 @@
         <v>5</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" s="9" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Embestida</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 2 de Vida.</t>
+        </is>
+      </c>
       <c r="L65" s="10" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customHeight="1">
@@ -3430,13 +3783,21 @@
         <v/>
       </c>
       <c r="H66" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="10" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>Refugio polar</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, a ninguno de tus dinosaurios le afectan los efectos del clima.</t>
+        </is>
+      </c>
       <c r="L66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
@@ -3476,8 +3837,16 @@
       <c r="I67" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J67" s="9" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>Grito de aviso</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>Al jugarlo, puedes llevarte a la mano un marginocéfalo de tu mazo.</t>
+        </is>
+      </c>
       <c r="L67" s="10" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
@@ -3512,13 +3881,21 @@
         <v/>
       </c>
       <c r="H68" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>Última llanura</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
+        </is>
+      </c>
       <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -3558,8 +3935,16 @@
       <c r="I69" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J69" s="9" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Cría acorazada</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>Gana +1 de Vida por cada tireóforo que tengas en juego, este incluido.</t>
+        </is>
+      </c>
       <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
@@ -3594,13 +3979,21 @@
         <v/>
       </c>
       <c r="H70" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J70" s="9" t="inlineStr"/>
-      <c r="K70" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>Ramoneo de orilla</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
+        </is>
+      </c>
       <c r="L70" s="10" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -3638,10 +4031,18 @@
         <v>2</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" s="9" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>Vigía de la gola</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego robas 1 carta.</t>
+        </is>
+      </c>
       <c r="L71" s="10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4261,6 +4662,646 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Las formas de habilidad que el motor ya sabe aplicar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Para pedir una habilidad nueva en «Mecánica nueva», lo más barato es describirla con una de estas formas y otros números: eso es un dato, no código. Una forma que no esté aquí se puede hacer igual, pero hay que escribirla en el motor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Forma</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Cartas</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Quiénes la llevan</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ejemplo de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Aura de clado</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Scanisaurus nazarowi, Monolophosaurus jiangi, Invictarx zephyri, Medusaceratops lokii, Atlasaurus imelakei, Edmontosaurus annectens</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, tus reptiles marinos ganan +1 de Ataque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>aura</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Aura de todo el bando</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Antarctosaurus wichmannianus</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Mientras esté en juego, a ninguno de tus dinosaurios le afectan los efectos del clima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>busca</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Busca en el mazo</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Athenar bermani, Sanjuansaurus gordilloi, Platyceratops tatarinovi, Liaoceratops yanzigouensis</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Al jugarlo, puedes llevarte a la mano una carta de evento de tu mazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>costeExtra</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Coste añadido</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Carnotaurus sastrei</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Para jugarlo tienes que descartar 2 cartas de tu mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>cuenta</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Contador por especie</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Dryosaurus altus, Stegosaurus stenops, Dromaeosaurus albertensis, Eosinopteryx brevipenna, Troodon formosus, Plateosauravus cullingworthi</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada Dryosaurus en juego, sea de quien sea y este incluido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>cuenta</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Contador por clado</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Titanoceratops ouranos, Bienosaurus lufengensis</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Gana +1 de Ataque por cada marginocéfalo que tengas en juego, este incluido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · curaHabitat</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Diplodocus carnegii, Apatosaurus louisae, Loricatosaurus priscus, Shuangmiaosaurus gilmorei</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego tu hábitat recupera 1 punto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · emboscada</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Ornitholestes hermanni, Ojoraptorsaurus boerei, Alaskacephale gangloffi</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego hiere en 2 al dinosaurio de enfrente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · fulmina</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Tyrannotitan chubutensis, Wendiceratops pinhornensis</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego manda al descarte 1 dinosaurio rival de hasta 4 de Vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · mueleRival + muelePropio</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Spinosaurus aegyptiacus, Mosasaurus hoffmannii</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 5 cartas del mazo de tu rival y 2 del tuyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · roba</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Huaxiadraco corollatus, Chasmosaurus belli</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego robas 1 carta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · manoRival</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Allosaurus fragilis</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 1 carta al azar de la mano de tu rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · muelePropio</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Ceratosaurus nasicornis</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 2 cartas de tu mazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>entrada</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Al entrar · mueleRival</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Suchomimus tenerensis</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Cuando entra en juego descarta 1 carta del mazo de tu rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>espinas</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Devuelve daño</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Stegoceras validum, Gargoyleosaurus parkpinorum</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Devuelve 2 de daño a quien lo hiera en combate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>inmune</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Inmunidad a CLIMA</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Torvosaurus tanneri, Nodosaurus textilis</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>No le afectan los efectos del clima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>inmune</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Inmunidad a EVENTO</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Riparovenator milnerae, Lokiceratops rangiformis</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>No le afectan las cartas de evento de tu rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>regenera</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Cura a los tuyos</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Maiasaura peeblesorum</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Al final de tu turno, todos tus dinosaurios recuperan 1 de Vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>regenera</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Se cura sola</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Camarasaurus grandis</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Al final de tu turno recupera 1 de Vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · CLIMA</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Halszkaraptor escuilliei, Tongtianlong limosus, Therizinosaurus cheloniformis</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Vida mientras haya un clima en el campo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · ALIADO_CON_VIDA</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Plesiopleurodon wellesi</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque si tienes en juego algún dinosaurio con más de 6 de Vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Condicional · HABITAT_DETRAS</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Rhinorex condrupus</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Gana +2 de Ataque mientras tu hábitat esté por debajo del de tu rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Umbral permanente</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Brachylophosaurus canadensis</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Si llegas a tener 3 Brachylophosaurus en juego, éste gana +6 de Ataque para siempre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4676,7 +5717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4743,10 +5784,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -4764,10 +5805,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -4785,10 +5826,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -4806,10 +5847,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.3</v>
+        <v>7.6</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -4827,10 +5868,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -4869,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -4888,7 +5929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4964,7 +6005,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4974,7 +6015,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5205,7 +6246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/RECOSTE.xlsx
+++ b/RECOSTE.xlsx
@@ -2113,7 +2113,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Llanura de inundación</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2140,7 +2140,7 @@
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Llanura de inundación</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2185,12 +2185,12 @@
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
+          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2230,7 +2230,7 @@
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2275,12 +2275,12 @@
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Ambos jugadores pierden 5 cartas del mazo</t>
+          <t>Ambos jugadores pierden 5 cartas del mazo cada turno.</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Sabana de helechos</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2320,7 +2320,7 @@
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Sabana de helechos</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bosque de coníferas ribereño</t>
+          <t>Bruma de valle</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
+          <t>+1 de Vida a todos los dinosaurios del campo, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -4162,19 +4162,19 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>heridas que curan los saurópodos</t>
+          <t>Vida a todos los del campo</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.bosqueCura</t>
+          <t>efectosCampo.canalVida</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -4182,32 +4182,26 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Canal fluvial trenzado</t>
+          <t>Carroña abundante</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Agua permanente: +1 de Vida a todos los dinosaurios del campo, y los ribereños pelean a gusto.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Vida a todos los del campo</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>efectosCampo.canalVida</t>
-        </is>
-      </c>
+          <t>no lleva número: es una regla, no una cifra</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -4215,26 +4209,32 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Carroña abundante</t>
+          <t>Competencia trófica</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>+3 Biomasa ahora mismo. El rival gana 1 Biomasa.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>no lleva número: es una regla, no una cifra</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
+          <t>Vida que se quita, a dos rivales</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>rasgos.competenciaVida</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -4242,25 +4242,25 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Competencia trófica</t>
+          <t>Crecida estacional</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>−2 de Vida a dos dinosaurios rivales que elijas.</t>
+          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Vida que se quita, a dos rivales</t>
+          <t>cambio de carta por turno y jugador</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>rasgos.competenciaVida</t>
+          <t>efectosCampo.llanuraReciclaPorTurno</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -4308,25 +4308,25 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Deriva árida</t>
+          <t>Estación de lluvias</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ambos jugadores pierden 5 cartas del mazo</t>
+          <t>Los saurópodos curan 1 herida al final de cada turno.</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>cartas de mazo que pierden los DOS</t>
+          <t>heridas que curan los saurópodos</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.aridezMazo</t>
+          <t>efectosCampo.bosqueCura</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Llanura de inundación</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Llanura de inundación</t>
+          <t>Monzón de verano</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Mientras esté en el campo, cada jugador puede cambiar una carta de su mano por otra del mazo, una vez por turno.</t>
+          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cambio de carta por turno y jugador</t>
+          <t>Biomasa por turno a los DOS</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.llanuraReciclaPorTurno</t>
+          <t>efectosCampo.sabanaBiomasa</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Sabana de helechos</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -4593,25 +4593,25 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Sabana de helechos</t>
+          <t>Sequía prolongada</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>+1 de Biomasa cada turno para los dos jugadores, mientras siga en el campo.</t>
+          <t>Ambos jugadores pierden 5 cartas del mazo cada turno.</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Biomasa por turno a los DOS</t>
+          <t>cartas de mazo que pierden los DOS</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>efectosCampo.sabanaBiomasa</t>
+          <t>efectosCampo.aridezMazo</t>
         </is>
       </c>
     </row>
